--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -733,14 +733,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>CRM, MSFT</t>
@@ -752,30 +752,30 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>49.35390647695785</v>
+        <v>49.35390788200862</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +30.29% / +40.48% / 0.00% | MSFT: -1.94% / +2.52% / -3.77%</t>
+          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14.53607258831178</v>
+        <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.741591325587522</v>
+        <v>-0.8341572647454831</v>
       </c>
       <c r="L3" t="n">
-        <v>16.46690220252861</v>
+        <v>16.46690178496608</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="O3" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="P3" t="n">
         <v>4.5</v>
@@ -795,13 +795,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>67.48699999999999</v>
+        <v>70.806</v>
       </c>
       <c r="V3" t="n">
-        <v>76.502</v>
+        <v>79.964</v>
       </c>
       <c r="W3" t="n">
-        <v>-21.347</v>
+        <v>-18.066</v>
       </c>
     </row>
     <row r="4">
@@ -820,14 +820,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -835,34 +835,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L4" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M4" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N4" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O4" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -882,13 +882,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V4" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="5">
@@ -907,14 +907,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -926,33 +926,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L5" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M5" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O5" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -969,13 +969,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V5" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="6">
@@ -994,14 +994,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -1009,34 +1009,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L6" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M6" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N6" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O6" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -1056,13 +1056,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V6" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="7">
@@ -1081,14 +1081,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -1100,33 +1100,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L7" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M7" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O7" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V7" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="8">
@@ -1168,14 +1168,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>CRM, MSFT</t>
@@ -1187,30 +1187,30 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.35390647695785</v>
+        <v>49.35390788200862</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +30.29% / +40.48% / 0.00% | MSFT: -1.94% / +2.52% / -3.77%</t>
+          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14.53607258831178</v>
+        <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.741591325587522</v>
+        <v>-0.8341572647454831</v>
       </c>
       <c r="L8" t="n">
-        <v>16.46690220252861</v>
+        <v>16.46690178496608</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="O8" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="P8" t="n">
         <v>4.5</v>
@@ -1230,13 +1230,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>67.48699999999999</v>
+        <v>70.806</v>
       </c>
       <c r="V8" t="n">
-        <v>76.502</v>
+        <v>79.964</v>
       </c>
       <c r="W8" t="n">
-        <v>-21.347</v>
+        <v>-18.066</v>
       </c>
     </row>
     <row r="9">
@@ -1255,14 +1255,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -1270,34 +1270,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L9" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M9" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O9" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -1317,13 +1317,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V9" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="10">
@@ -1342,14 +1342,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -1361,33 +1361,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L10" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M10" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O10" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1404,13 +1404,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V10" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="11">
@@ -1429,28 +1429,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>11.64377774832819</v>
+        <v>11.64377880826557</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>6.729893400376863</v>
+        <v>6.729894491660082</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2318596464697897</v>
+        <v>0.231855628775679</v>
       </c>
       <c r="L11" t="n">
-        <v>5.137940484107217</v>
+        <v>5.137942413230245</v>
       </c>
       <c r="M11" t="n">
         <v>38.88888888888889</v>
@@ -1504,14 +1504,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>COP, CRM</t>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.926860223931252</v>
+        <v>5.926857774740779</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +9.96% / +11.54% / 0.00% | CRM: +25.97% / +35.83% / -3.85%</t>
+          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-1.38161292896819</v>
+        <v>-1.381618466137391</v>
       </c>
       <c r="K12" t="n">
-        <v>20.08996420183564</v>
+        <v>22.95873098582635</v>
       </c>
       <c r="L12" t="n">
-        <v>10.56545305189324</v>
+        <v>10.56544794881541</v>
       </c>
       <c r="M12" t="n">
         <v>38.88888888888889</v>
@@ -1549,7 +1549,7 @@
         <v>65.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1566,13 +1566,13 @@
         <v>7.071</v>
       </c>
       <c r="U12" t="n">
-        <v>31.264</v>
+        <v>34.4</v>
       </c>
       <c r="V12" t="n">
-        <v>32.891</v>
+        <v>36.065</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.835</v>
+        <v>-0.699</v>
       </c>
     </row>
     <row r="13">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -1610,30 +1610,30 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K13" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L13" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P13" t="n">
         <v>2.7</v>
@@ -1653,13 +1653,13 @@
         <v>13.226</v>
       </c>
       <c r="U13" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V13" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1678,14 +1678,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -1697,30 +1697,30 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K14" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L14" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M14" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P14" t="n">
         <v>2.7</v>
@@ -1740,13 +1740,13 @@
         <v>13.226</v>
       </c>
       <c r="U14" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V14" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1891,14 +1891,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>CRM, MSFT</t>
@@ -1910,30 +1910,30 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>49.35390647695785</v>
+        <v>49.35390788200862</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +30.29% / +40.48% / 0.00% | MSFT: -1.94% / +2.52% / -3.77%</t>
+          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14.53607258831178</v>
+        <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.741591325587522</v>
+        <v>-0.8341572647454831</v>
       </c>
       <c r="L18" t="n">
-        <v>16.46690220252861</v>
+        <v>16.46690178496608</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="O18" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="P18" t="n">
         <v>4.5</v>
@@ -1953,13 +1953,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>67.48699999999999</v>
+        <v>70.806</v>
       </c>
       <c r="V18" t="n">
-        <v>76.502</v>
+        <v>79.964</v>
       </c>
       <c r="W18" t="n">
-        <v>-21.347</v>
+        <v>-18.066</v>
       </c>
     </row>
     <row r="19">
@@ -1980,14 +1980,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -1995,34 +1995,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L19" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M19" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N19" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O19" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -2042,13 +2042,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V19" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="20">
@@ -2069,14 +2069,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -2088,33 +2088,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L20" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M20" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O20" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V20" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W20" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="21">
@@ -2158,14 +2158,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -2177,30 +2177,30 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K21" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L21" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M21" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P21" t="n">
         <v>2.7</v>
@@ -2220,13 +2220,13 @@
         <v>13.226</v>
       </c>
       <c r="U21" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V21" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -2266,30 +2266,30 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K22" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L22" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M22" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P22" t="n">
         <v>2.7</v>
@@ -2309,13 +2309,13 @@
         <v>13.226</v>
       </c>
       <c r="U22" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V22" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2336,28 +2336,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>11.64377774832819</v>
+        <v>11.64377880826557</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>6.729893400376863</v>
+        <v>6.729894491660082</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2318596464697897</v>
+        <v>0.231855628775679</v>
       </c>
       <c r="L23" t="n">
-        <v>5.137940484107217</v>
+        <v>5.137942413230245</v>
       </c>
       <c r="M23" t="n">
         <v>38.88888888888889</v>
@@ -2413,14 +2413,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>COP, CRM</t>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.926860223931252</v>
+        <v>5.926857774740779</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COP: +9.96% / +11.54% / 0.00% | CRM: +25.97% / +35.83% / -3.85%</t>
+          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-1.38161292896819</v>
+        <v>-1.381618466137391</v>
       </c>
       <c r="K24" t="n">
-        <v>20.08996420183564</v>
+        <v>22.95873098582635</v>
       </c>
       <c r="L24" t="n">
-        <v>10.56545305189324</v>
+        <v>10.56544794881541</v>
       </c>
       <c r="M24" t="n">
         <v>38.88888888888889</v>
@@ -2458,7 +2458,7 @@
         <v>65.7</v>
       </c>
       <c r="P24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2475,13 +2475,13 @@
         <v>7.071</v>
       </c>
       <c r="U24" t="n">
-        <v>31.264</v>
+        <v>34.4</v>
       </c>
       <c r="V24" t="n">
-        <v>32.891</v>
+        <v>36.065</v>
       </c>
       <c r="W24" t="n">
-        <v>-3.835</v>
+        <v>-0.699</v>
       </c>
     </row>
   </sheetData>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>CRM, MSFT</t>
@@ -2690,30 +2690,30 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>49.35390647695785</v>
+        <v>49.35390788200862</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +30.29% / +40.48% / 0.00% | MSFT: -1.94% / +2.52% / -3.77%</t>
+          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14.53607258831178</v>
+        <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.741591325587522</v>
+        <v>-0.8341572647454831</v>
       </c>
       <c r="L3" t="n">
-        <v>16.46690220252861</v>
+        <v>16.46690178496608</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="O3" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="P3" t="n">
         <v>4.5</v>
@@ -2733,13 +2733,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>67.48699999999999</v>
+        <v>70.806</v>
       </c>
       <c r="V3" t="n">
-        <v>76.502</v>
+        <v>79.964</v>
       </c>
       <c r="W3" t="n">
-        <v>-21.347</v>
+        <v>-18.066</v>
       </c>
     </row>
     <row r="4">
@@ -2758,14 +2758,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -2773,34 +2773,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L4" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M4" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N4" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O4" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -2820,13 +2820,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V4" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="5">
@@ -2845,14 +2845,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -2864,33 +2864,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L5" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M5" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O5" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -2907,13 +2907,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V5" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="6">
@@ -2932,14 +2932,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -2947,34 +2947,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L6" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M6" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N6" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O6" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -2994,13 +2994,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V6" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="7">
@@ -3019,14 +3019,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -3038,33 +3038,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L7" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M7" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O7" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V7" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="8">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>CRM, MSFT</t>
@@ -3125,30 +3125,30 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.35390647695785</v>
+        <v>49.35390788200862</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +30.29% / +40.48% / 0.00% | MSFT: -1.94% / +2.52% / -3.77%</t>
+          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14.53607258831178</v>
+        <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.741591325587522</v>
+        <v>-0.8341572647454831</v>
       </c>
       <c r="L8" t="n">
-        <v>16.46690220252861</v>
+        <v>16.46690178496608</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="O8" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="P8" t="n">
         <v>4.5</v>
@@ -3168,13 +3168,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>67.48699999999999</v>
+        <v>70.806</v>
       </c>
       <c r="V8" t="n">
-        <v>76.502</v>
+        <v>79.964</v>
       </c>
       <c r="W8" t="n">
-        <v>-21.347</v>
+        <v>-18.066</v>
       </c>
     </row>
     <row r="9">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -3208,34 +3208,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L9" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M9" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O9" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -3255,13 +3255,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V9" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="10">
@@ -3280,14 +3280,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -3299,33 +3299,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L10" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M10" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O10" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -3342,13 +3342,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V10" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="11">
@@ -3367,28 +3367,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>11.64377774832819</v>
+        <v>11.64377880826557</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>6.729893400376863</v>
+        <v>6.729894491660082</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2318596464697897</v>
+        <v>0.231855628775679</v>
       </c>
       <c r="L11" t="n">
-        <v>5.137940484107217</v>
+        <v>5.137942413230245</v>
       </c>
       <c r="M11" t="n">
         <v>38.88888888888889</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>COP, CRM</t>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.926860223931252</v>
+        <v>5.926857774740779</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +9.96% / +11.54% / 0.00% | CRM: +25.97% / +35.83% / -3.85%</t>
+          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-1.38161292896819</v>
+        <v>-1.381618466137391</v>
       </c>
       <c r="K12" t="n">
-        <v>20.08996420183564</v>
+        <v>22.95873098582635</v>
       </c>
       <c r="L12" t="n">
-        <v>10.56545305189324</v>
+        <v>10.56544794881541</v>
       </c>
       <c r="M12" t="n">
         <v>38.88888888888889</v>
@@ -3487,7 +3487,7 @@
         <v>65.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3504,13 +3504,13 @@
         <v>7.071</v>
       </c>
       <c r="U12" t="n">
-        <v>31.264</v>
+        <v>34.4</v>
       </c>
       <c r="V12" t="n">
-        <v>32.891</v>
+        <v>36.065</v>
       </c>
       <c r="W12" t="n">
-        <v>-3.835</v>
+        <v>-0.699</v>
       </c>
     </row>
     <row r="13">
@@ -3529,14 +3529,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -3548,30 +3548,30 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K13" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L13" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P13" t="n">
         <v>2.7</v>
@@ -3591,13 +3591,13 @@
         <v>13.226</v>
       </c>
       <c r="U13" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V13" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3616,14 +3616,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -3635,30 +3635,30 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K14" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L14" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M14" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P14" t="n">
         <v>2.7</v>
@@ -3678,13 +3678,13 @@
         <v>13.226</v>
       </c>
       <c r="U14" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V14" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -3829,14 +3829,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>CRM, MSFT</t>
@@ -3848,30 +3848,30 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>49.35390647695785</v>
+        <v>49.35390788200862</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +30.29% / +40.48% / 0.00% | MSFT: -1.94% / +2.52% / -3.77%</t>
+          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14.53607258831178</v>
+        <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.741591325587522</v>
+        <v>-0.8341572647454831</v>
       </c>
       <c r="L18" t="n">
-        <v>16.46690220252861</v>
+        <v>16.46690178496608</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="O18" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="P18" t="n">
         <v>4.5</v>
@@ -3891,13 +3891,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>67.48699999999999</v>
+        <v>70.806</v>
       </c>
       <c r="V18" t="n">
-        <v>76.502</v>
+        <v>79.964</v>
       </c>
       <c r="W18" t="n">
-        <v>-21.347</v>
+        <v>-18.066</v>
       </c>
     </row>
     <row r="19">
@@ -3918,14 +3918,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>GOOGL, NVDA</t>
@@ -3933,34 +3933,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-11</t>
+          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>46.89202625087505</v>
+        <v>46.89202291173533</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GOOGL: -0.02% / +0.00% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>20.23942829156833</v>
+        <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.058471244066974</v>
+        <v>-3.933158349512877</v>
       </c>
       <c r="L19" t="n">
-        <v>8.076884481142056</v>
+        <v>8.076882947230402</v>
       </c>
       <c r="M19" t="n">
         <v>72.22222222222221</v>
       </c>
       <c r="N19" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="O19" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -3980,13 +3980,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>30.124</v>
+        <v>28.95</v>
       </c>
       <c r="V19" t="n">
-        <v>16.398</v>
+        <v>15.348</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.675</v>
+        <v>-6.849</v>
       </c>
     </row>
     <row r="20">
@@ -4007,14 +4007,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>AMZN, COP</t>
@@ -4026,33 +4026,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>44.24447509506124</v>
+        <v>44.24447097072779</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>16.32709285641736</v>
+        <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.100625610711938</v>
+        <v>-3.257815072809134</v>
       </c>
       <c r="L20" t="n">
-        <v>8.338917136326652</v>
+        <v>8.338915824512183</v>
       </c>
       <c r="M20" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="O20" t="n">
-        <v>57.1</v>
+        <v>58.2</v>
       </c>
       <c r="P20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -4069,13 +4069,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>35.102</v>
+        <v>34.91</v>
       </c>
       <c r="V20" t="n">
-        <v>25.164</v>
+        <v>24.961</v>
       </c>
       <c r="W20" t="n">
-        <v>-4.323</v>
+        <v>-4.543</v>
       </c>
     </row>
     <row r="21">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -4115,30 +4115,30 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K21" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L21" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M21" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P21" t="n">
         <v>2.7</v>
@@ -4158,13 +4158,13 @@
         <v>13.226</v>
       </c>
       <c r="U21" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V21" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -4185,14 +4185,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>COP, OXY</t>
@@ -4204,30 +4204,30 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19.02433694994408</v>
+        <v>19.02433828301018</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COP: -0.02% / +0.00% / 0.00% | OXY: -0.02% / +0.00% / 0.00%</t>
+          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.7593497103236424</v>
+        <v>-0.759353416073727</v>
       </c>
       <c r="K22" t="n">
-        <v>15.58902006101675</v>
+        <v>17.28043431801836</v>
       </c>
       <c r="L22" t="n">
-        <v>11.12668877665739</v>
+        <v>11.1266875</v>
       </c>
       <c r="M22" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>53.7</v>
+        <v>55</v>
       </c>
       <c r="P22" t="n">
         <v>2.7</v>
@@ -4247,13 +4247,13 @@
         <v>13.226</v>
       </c>
       <c r="U22" t="n">
-        <v>68.61499999999999</v>
+        <v>71.117</v>
       </c>
       <c r="V22" t="n">
-        <v>71.941</v>
+        <v>74.45699999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>-3.032</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -4274,28 +4274,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>11.64377774832819</v>
+        <v>11.64377880826557</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>6.729893400376863</v>
+        <v>6.729894491660082</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2318596464697897</v>
+        <v>0.231855628775679</v>
       </c>
       <c r="L23" t="n">
-        <v>5.137940484107217</v>
+        <v>5.137942413230245</v>
       </c>
       <c r="M23" t="n">
         <v>38.88888888888889</v>
@@ -4351,14 +4351,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>COP, CRM</t>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.926860223931252</v>
+        <v>5.926857774740779</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COP: +9.96% / +11.54% / 0.00% | CRM: +25.97% / +35.83% / -3.85%</t>
+          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-1.38161292896819</v>
+        <v>-1.381618466137391</v>
       </c>
       <c r="K24" t="n">
-        <v>20.08996420183564</v>
+        <v>22.95873098582635</v>
       </c>
       <c r="L24" t="n">
-        <v>10.56545305189324</v>
+        <v>10.56544794881541</v>
       </c>
       <c r="M24" t="n">
         <v>38.88888888888889</v>
@@ -4396,7 +4396,7 @@
         <v>65.7</v>
       </c>
       <c r="P24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         <v>7.071</v>
       </c>
       <c r="U24" t="n">
-        <v>31.264</v>
+        <v>34.4</v>
       </c>
       <c r="V24" t="n">
-        <v>32.891</v>
+        <v>36.065</v>
       </c>
       <c r="W24" t="n">
-        <v>-3.835</v>
+        <v>-0.699</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -574,7 +574,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
+          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8341572647454831</v>
+        <v>-0.779711711691955</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -772,13 +772,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O3" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -795,13 +795,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>70.806</v>
+        <v>71.015</v>
       </c>
       <c r="V3" t="n">
-        <v>79.964</v>
+        <v>80.063</v>
       </c>
       <c r="W3" t="n">
-        <v>-18.066</v>
+        <v>-17.984</v>
       </c>
     </row>
     <row r="4">
@@ -820,22 +820,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -859,10 +859,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N4" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O4" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -882,13 +882,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V4" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="5">
@@ -907,12 +907,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -946,7 +946,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O5" t="n">
         <v>58.2</v>
@@ -969,13 +969,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V5" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="6">
@@ -994,22 +994,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -1033,10 +1033,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N6" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O6" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -1056,13 +1056,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V6" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="7">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -1120,7 +1120,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O7" t="n">
         <v>58.2</v>
@@ -1143,13 +1143,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V7" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="8">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
+          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8341572647454831</v>
+        <v>-0.779711711691955</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -1207,13 +1207,13 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O8" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1230,13 +1230,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>70.806</v>
+        <v>71.015</v>
       </c>
       <c r="V8" t="n">
-        <v>79.964</v>
+        <v>80.063</v>
       </c>
       <c r="W8" t="n">
-        <v>-18.066</v>
+        <v>-17.984</v>
       </c>
     </row>
     <row r="9">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -1294,10 +1294,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O9" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -1317,13 +1317,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V9" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="10">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -1381,7 +1381,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O10" t="n">
         <v>58.2</v>
@@ -1404,13 +1404,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V10" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="11">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="O11" t="n">
         <v>58.3</v>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
+          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.381618466137391</v>
       </c>
       <c r="K12" t="n">
-        <v>22.95873098582635</v>
+        <v>24.87307105054877</v>
       </c>
       <c r="L12" t="n">
         <v>10.56544794881541</v>
@@ -1543,13 +1543,13 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="O12" t="n">
         <v>65.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1566,13 +1566,13 @@
         <v>7.071</v>
       </c>
       <c r="U12" t="n">
-        <v>34.4</v>
+        <v>36.493</v>
       </c>
       <c r="V12" t="n">
-        <v>36.065</v>
+        <v>38.184</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1614,14 +1614,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K13" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L13" t="n">
         <v>11.1266875</v>
@@ -1630,7 +1630,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O13" t="n">
         <v>55</v>
@@ -1653,13 +1653,13 @@
         <v>13.226</v>
       </c>
       <c r="U13" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V13" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K14" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L14" t="n">
         <v>11.1266875</v>
@@ -1717,7 +1717,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O14" t="n">
         <v>55</v>
@@ -1740,13 +1740,13 @@
         <v>13.226</v>
       </c>
       <c r="U14" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V14" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
+          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8341572647454831</v>
+        <v>-0.779711711691955</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -1930,13 +1930,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O18" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="P18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1953,13 +1953,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>70.806</v>
+        <v>71.015</v>
       </c>
       <c r="V18" t="n">
-        <v>79.964</v>
+        <v>80.063</v>
       </c>
       <c r="W18" t="n">
-        <v>-18.066</v>
+        <v>-17.984</v>
       </c>
     </row>
     <row r="19">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2003,14 +2003,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -2019,10 +2019,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N19" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O19" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -2042,13 +2042,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V19" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="20">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -2108,7 +2108,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O20" t="n">
         <v>58.2</v>
@@ -2131,13 +2131,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V20" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W20" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="21">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2181,14 +2181,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K21" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L21" t="n">
         <v>11.1266875</v>
@@ -2197,7 +2197,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O21" t="n">
         <v>55</v>
@@ -2220,13 +2220,13 @@
         <v>13.226</v>
       </c>
       <c r="U21" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V21" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2270,14 +2270,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K22" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L22" t="n">
         <v>11.1266875</v>
@@ -2286,7 +2286,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O22" t="n">
         <v>55</v>
@@ -2309,13 +2309,13 @@
         <v>13.226</v>
       </c>
       <c r="U22" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V22" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N23" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="O23" t="n">
         <v>58.3</v>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
+          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-1.381618466137391</v>
       </c>
       <c r="K24" t="n">
-        <v>22.95873098582635</v>
+        <v>24.87307105054877</v>
       </c>
       <c r="L24" t="n">
         <v>10.56544794881541</v>
@@ -2452,13 +2452,13 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N24" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="O24" t="n">
         <v>65.7</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2475,13 +2475,13 @@
         <v>7.071</v>
       </c>
       <c r="U24" t="n">
-        <v>34.4</v>
+        <v>36.493</v>
       </c>
       <c r="V24" t="n">
-        <v>36.065</v>
+        <v>38.184</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.699</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2512,7 +2512,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2694,14 +2694,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
+          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8341572647454831</v>
+        <v>-0.779711711691955</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -2710,13 +2710,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O3" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>70.806</v>
+        <v>71.015</v>
       </c>
       <c r="V3" t="n">
-        <v>79.964</v>
+        <v>80.063</v>
       </c>
       <c r="W3" t="n">
-        <v>-18.066</v>
+        <v>-17.984</v>
       </c>
     </row>
     <row r="4">
@@ -2758,22 +2758,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2781,14 +2781,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -2797,10 +2797,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N4" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O4" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -2820,13 +2820,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V4" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="5">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2868,14 +2868,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -2884,7 +2884,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O5" t="n">
         <v>58.2</v>
@@ -2907,13 +2907,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V5" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="6">
@@ -2932,22 +2932,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -2971,10 +2971,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N6" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O6" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -2994,13 +2994,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V6" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="7">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -3058,7 +3058,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O7" t="n">
         <v>58.2</v>
@@ -3081,13 +3081,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V7" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="8">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
+          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8341572647454831</v>
+        <v>-0.779711711691955</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -3145,13 +3145,13 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O8" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -3168,13 +3168,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>70.806</v>
+        <v>71.015</v>
       </c>
       <c r="V8" t="n">
-        <v>79.964</v>
+        <v>80.063</v>
       </c>
       <c r="W8" t="n">
-        <v>-18.066</v>
+        <v>-17.984</v>
       </c>
     </row>
     <row r="9">
@@ -3193,22 +3193,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -3216,14 +3216,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -3232,10 +3232,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O9" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -3255,13 +3255,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V9" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="10">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3303,14 +3303,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -3319,7 +3319,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O10" t="n">
         <v>58.2</v>
@@ -3342,13 +3342,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V10" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="11">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="O11" t="n">
         <v>58.3</v>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3465,14 +3465,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
+          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.381618466137391</v>
       </c>
       <c r="K12" t="n">
-        <v>22.95873098582635</v>
+        <v>24.87307105054877</v>
       </c>
       <c r="L12" t="n">
         <v>10.56544794881541</v>
@@ -3481,13 +3481,13 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N12" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="O12" t="n">
         <v>65.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3504,13 +3504,13 @@
         <v>7.071</v>
       </c>
       <c r="U12" t="n">
-        <v>34.4</v>
+        <v>36.493</v>
       </c>
       <c r="V12" t="n">
-        <v>36.065</v>
+        <v>38.184</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K13" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L13" t="n">
         <v>11.1266875</v>
@@ -3568,7 +3568,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O13" t="n">
         <v>55</v>
@@ -3591,13 +3591,13 @@
         <v>13.226</v>
       </c>
       <c r="U13" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V13" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3639,14 +3639,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K14" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L14" t="n">
         <v>11.1266875</v>
@@ -3655,7 +3655,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O14" t="n">
         <v>55</v>
@@ -3678,13 +3678,13 @@
         <v>13.226</v>
       </c>
       <c r="U14" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V14" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3852,14 +3852,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +34.67% / +40.48% / 0.00% | MSFT: +0.02% / +2.52% / -3.77%</t>
+          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8341572647454831</v>
+        <v>-0.779711711691955</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -3868,13 +3868,13 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="O18" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="P18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>70.806</v>
+        <v>71.015</v>
       </c>
       <c r="V18" t="n">
-        <v>79.964</v>
+        <v>80.063</v>
       </c>
       <c r="W18" t="n">
-        <v>-18.066</v>
+        <v>-17.984</v>
       </c>
     </row>
     <row r="19">
@@ -3918,22 +3918,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GOOGL, NVDA</t>
+          <t>MU, NVDA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOOGL: 2026-09-11 | NVDA: 2026-09-14</t>
+          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GOOGL: +2.21% / +2.59% / 0.00% | NVDA: -0.02% / +0.00% / 0.00%</t>
+          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.933158349512877</v>
+        <v>-3.986162718867126</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -3957,10 +3957,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N19" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="O19" t="n">
-        <v>60.7</v>
+        <v>61.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -3980,13 +3980,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>28.95</v>
+        <v>28.879</v>
       </c>
       <c r="V19" t="n">
-        <v>15.348</v>
+        <v>15.285</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.849</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="20">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4030,14 +4030,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -1.33% / +0.00% / -2.35% | COP: +0.97% / +1.79% / 0.00%</t>
+          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.257815072809134</v>
+        <v>-3.437760804543488</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -4046,7 +4046,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="O20" t="n">
         <v>58.2</v>
@@ -4069,13 +4069,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>34.91</v>
+        <v>35.428</v>
       </c>
       <c r="V20" t="n">
-        <v>24.961</v>
+        <v>24.729</v>
       </c>
       <c r="W20" t="n">
-        <v>-4.543</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="21">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4119,14 +4119,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K21" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L21" t="n">
         <v>11.1266875</v>
@@ -4135,7 +4135,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N21" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O21" t="n">
         <v>55</v>
@@ -4158,13 +4158,13 @@
         <v>13.226</v>
       </c>
       <c r="U21" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V21" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4208,14 +4208,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COP: +0.97% / +1.79% / 0.00% | OXY: +1.92% / +2.46% / 0.00%</t>
+          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>-0.759353416073727</v>
       </c>
       <c r="K22" t="n">
-        <v>17.28043431801836</v>
+        <v>18.67914553579049</v>
       </c>
       <c r="L22" t="n">
         <v>11.1266875</v>
@@ -4224,7 +4224,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N22" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="O22" t="n">
         <v>55</v>
@@ -4247,13 +4247,13 @@
         <v>13.226</v>
       </c>
       <c r="U22" t="n">
-        <v>71.117</v>
+        <v>73.274</v>
       </c>
       <c r="V22" t="n">
-        <v>74.45699999999999</v>
+        <v>76.53700000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4301,7 +4301,7 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N23" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="O23" t="n">
         <v>58.3</v>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4374,14 +4374,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COP: +11.37% / +12.28% / 0.00% | CRM: +30.21% / +35.83% / -3.85%</t>
+          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>-1.381618466137391</v>
       </c>
       <c r="K24" t="n">
-        <v>22.95873098582635</v>
+        <v>24.87307105054877</v>
       </c>
       <c r="L24" t="n">
         <v>10.56544794881541</v>
@@ -4390,13 +4390,13 @@
         <v>38.88888888888889</v>
       </c>
       <c r="N24" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="O24" t="n">
         <v>65.7</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         <v>7.071</v>
       </c>
       <c r="U24" t="n">
-        <v>34.4</v>
+        <v>36.493</v>
       </c>
       <c r="V24" t="n">
-        <v>36.065</v>
+        <v>38.184</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.699</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -733,22 +733,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CRM, MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CRM: 2026-08-17 | MSFT: 2026-08-27</t>
+          <t>CRM: 2026-08-17</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
+          <t>CRM: +31.28% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.779711711691955</v>
+        <v>-2.702068946073233</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -772,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="O3" t="n">
         <v>47.1</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>19.429</v>
@@ -795,13 +795,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>71.015</v>
+        <v>64.833</v>
       </c>
       <c r="V3" t="n">
-        <v>80.063</v>
+        <v>76.574</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.984</v>
+        <v>-20.933</v>
       </c>
     </row>
     <row r="4">
@@ -820,12 +820,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -859,10 +859,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N4" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O4" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -882,13 +882,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V4" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="5">
@@ -907,12 +907,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -946,10 +946,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O5" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P5" t="n">
         <v>4.3</v>
@@ -969,13 +969,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V5" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="6">
@@ -994,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -1033,10 +1033,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N6" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O6" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -1056,13 +1056,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V6" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="7">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -1120,10 +1120,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O7" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P7" t="n">
         <v>4.3</v>
@@ -1143,13 +1143,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V7" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="8">
@@ -1168,22 +1168,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CRM, MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CRM: 2026-08-17 | MSFT: 2026-08-27</t>
+          <t>CRM: 2026-08-17</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
+          <t>CRM: +31.28% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.779711711691955</v>
+        <v>-2.702068946073233</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -1207,7 +1207,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="O8" t="n">
         <v>47.1</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>19.429</v>
@@ -1230,13 +1230,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>71.015</v>
+        <v>64.833</v>
       </c>
       <c r="V8" t="n">
-        <v>80.063</v>
+        <v>76.574</v>
       </c>
       <c r="W8" t="n">
-        <v>-17.984</v>
+        <v>-20.933</v>
       </c>
     </row>
     <row r="9">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -1294,10 +1294,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O9" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -1317,13 +1317,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V9" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="10">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -1381,10 +1381,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O10" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
@@ -1404,13 +1404,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V10" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="11">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1527,14 +1527,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
+          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.381618466137391</v>
       </c>
       <c r="K12" t="n">
-        <v>24.87307105054877</v>
+        <v>19.64112930541479</v>
       </c>
       <c r="L12" t="n">
         <v>10.56544794881541</v>
@@ -1566,13 +1566,13 @@
         <v>7.071</v>
       </c>
       <c r="U12" t="n">
-        <v>36.493</v>
+        <v>30.774</v>
       </c>
       <c r="V12" t="n">
-        <v>38.184</v>
+        <v>32.394</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-4.339</v>
       </c>
     </row>
     <row r="13">
@@ -1586,80 +1586,68 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>COP, OXY</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>19.02433828301018</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
-        </is>
-      </c>
+        <v>-5.737726850587677</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-0.759353416073727</v>
+        <v>-15.51355971349434</v>
       </c>
       <c r="K13" t="n">
-        <v>18.67914553579049</v>
+        <v>14.16765759127694</v>
       </c>
       <c r="L13" t="n">
-        <v>11.1266875</v>
+        <v>22.83624131316222</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>74.2</v>
+        <v>47.7</v>
       </c>
       <c r="O13" t="n">
-        <v>55</v>
+        <v>56.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>13.226</v>
+        <v>15.881</v>
       </c>
       <c r="T13" t="n">
-        <v>13.226</v>
+        <v>13.069</v>
       </c>
       <c r="U13" t="n">
-        <v>73.274</v>
+        <v>75.04900000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>76.53700000000001</v>
+        <v>98.842</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="14">
@@ -1673,80 +1661,68 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>COP, OXY</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>19.02433828301018</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
-        </is>
-      </c>
+        <v>-4.039576813106816</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-0.759353416073727</v>
+        <v>-15.51412294404569</v>
       </c>
       <c r="K14" t="n">
-        <v>18.67914553579049</v>
+        <v>14.16764711666048</v>
       </c>
       <c r="L14" t="n">
-        <v>11.1266875</v>
+        <v>22.8370162826819</v>
       </c>
       <c r="M14" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>74.2</v>
+        <v>45.2</v>
       </c>
       <c r="O14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>13.226</v>
+        <v>15.882</v>
       </c>
       <c r="T14" t="n">
-        <v>13.226</v>
+        <v>12.892</v>
       </c>
       <c r="U14" t="n">
-        <v>73.274</v>
+        <v>56.587</v>
       </c>
       <c r="V14" t="n">
-        <v>76.53700000000001</v>
+        <v>77.873</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="16">
@@ -1891,22 +1867,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRM, MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CRM: 2026-08-17 | MSFT: 2026-08-27</t>
+          <t>CRM: 2026-08-17</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1914,14 +1890,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
+          <t>CRM: +31.28% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.779711711691955</v>
+        <v>-2.702068946073233</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -1930,7 +1906,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="O18" t="n">
         <v>47.1</v>
@@ -1944,7 +1920,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>19.429</v>
@@ -1953,13 +1929,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>71.015</v>
+        <v>64.833</v>
       </c>
       <c r="V18" t="n">
-        <v>80.063</v>
+        <v>76.574</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.984</v>
+        <v>-20.933</v>
       </c>
     </row>
     <row r="19">
@@ -1980,12 +1956,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2003,14 +1979,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -2019,10 +1995,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N19" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O19" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -2042,13 +2018,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V19" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="20">
@@ -2069,12 +2045,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2092,14 +2068,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -2108,10 +2084,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O20" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P20" t="n">
         <v>4.3</v>
@@ -2131,102 +2107,90 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V20" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W20" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>COP, OXY</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>19.02433828301018</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
-        </is>
-      </c>
+        <v>11.64377880826557</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>-0.759353416073727</v>
+        <v>6.729894491660082</v>
       </c>
       <c r="K21" t="n">
-        <v>18.67914553579049</v>
+        <v>0.231855628775679</v>
       </c>
       <c r="L21" t="n">
-        <v>11.1266875</v>
+        <v>5.137942413230245</v>
       </c>
       <c r="M21" t="n">
-        <v>77.77777777777779</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>74.2</v>
+        <v>17.9</v>
       </c>
       <c r="O21" t="n">
-        <v>55</v>
+        <v>58.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>13.226</v>
+        <v>8.561</v>
       </c>
       <c r="T21" t="n">
-        <v>13.226</v>
+        <v>8.561</v>
       </c>
       <c r="U21" t="n">
-        <v>73.274</v>
+        <v>46.205</v>
       </c>
       <c r="V21" t="n">
-        <v>76.53700000000001</v>
+        <v>39.702</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-3.629</v>
       </c>
     </row>
     <row r="22">
@@ -2237,62 +2201,62 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COP, OXY</t>
+          <t>COP, CRM</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
+          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19.02433828301018</v>
+        <v>5.926857774740779</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
+          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.759353416073727</v>
+        <v>-1.381618466137391</v>
       </c>
       <c r="K22" t="n">
-        <v>18.67914553579049</v>
+        <v>19.64112930541479</v>
       </c>
       <c r="L22" t="n">
-        <v>11.1266875</v>
+        <v>10.56544794881541</v>
       </c>
       <c r="M22" t="n">
-        <v>77.77777777777779</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="N22" t="n">
-        <v>74.2</v>
+        <v>17.4</v>
       </c>
       <c r="O22" t="n">
-        <v>55</v>
+        <v>65.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2303,25 +2267,25 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>13.226</v>
+        <v>7.071</v>
       </c>
       <c r="T22" t="n">
-        <v>13.226</v>
+        <v>7.071</v>
       </c>
       <c r="U22" t="n">
-        <v>73.274</v>
+        <v>30.774</v>
       </c>
       <c r="V22" t="n">
-        <v>76.53700000000001</v>
+        <v>32.394</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-4.339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2331,45 +2295,45 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>11.64377880826557</v>
+        <v>-4.039576813106816</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>6.729894491660082</v>
+        <v>-15.51412294404569</v>
       </c>
       <c r="K23" t="n">
-        <v>0.231855628775679</v>
+        <v>14.16764711666048</v>
       </c>
       <c r="L23" t="n">
-        <v>5.137942413230245</v>
+        <v>22.8370162826819</v>
       </c>
       <c r="M23" t="n">
-        <v>38.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>17.9</v>
+        <v>45.2</v>
       </c>
       <c r="O23" t="n">
-        <v>58.3</v>
+        <v>56</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2380,19 +2344,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>8.561</v>
+        <v>15.882</v>
       </c>
       <c r="T23" t="n">
-        <v>8.561</v>
+        <v>12.892</v>
       </c>
       <c r="U23" t="n">
-        <v>46.205</v>
+        <v>56.587</v>
       </c>
       <c r="V23" t="n">
-        <v>39.702</v>
+        <v>77.873</v>
       </c>
       <c r="W23" t="n">
-        <v>-3.629</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="24">
@@ -2403,85 +2367,73 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>5.926857774740779</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
-        </is>
-      </c>
+        <v>-5.737726850587677</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-1.381618466137391</v>
+        <v>-15.51355971349434</v>
       </c>
       <c r="K24" t="n">
-        <v>24.87307105054877</v>
+        <v>14.16765759127694</v>
       </c>
       <c r="L24" t="n">
-        <v>10.56544794881541</v>
+        <v>22.83624131316222</v>
       </c>
       <c r="M24" t="n">
-        <v>38.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>17.4</v>
+        <v>47.7</v>
       </c>
       <c r="O24" t="n">
-        <v>65.7</v>
+        <v>56.2</v>
       </c>
       <c r="P24" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>7.071</v>
+        <v>15.881</v>
       </c>
       <c r="T24" t="n">
-        <v>7.071</v>
+        <v>13.069</v>
       </c>
       <c r="U24" t="n">
-        <v>36.493</v>
+        <v>75.04900000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>38.184</v>
+        <v>98.842</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-5.859</v>
       </c>
     </row>
   </sheetData>
@@ -2671,22 +2623,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CRM, MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CRM: 2026-08-17 | MSFT: 2026-08-27</t>
+          <t>CRM: 2026-08-17</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2694,14 +2646,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
+          <t>CRM: +31.28% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.779711711691955</v>
+        <v>-2.702068946073233</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -2710,7 +2662,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="O3" t="n">
         <v>47.1</v>
@@ -2724,7 +2676,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>19.429</v>
@@ -2733,13 +2685,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>71.015</v>
+        <v>64.833</v>
       </c>
       <c r="V3" t="n">
-        <v>80.063</v>
+        <v>76.574</v>
       </c>
       <c r="W3" t="n">
-        <v>-17.984</v>
+        <v>-20.933</v>
       </c>
     </row>
     <row r="4">
@@ -2758,12 +2710,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2781,14 +2733,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -2797,10 +2749,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N4" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O4" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -2820,13 +2772,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V4" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="5">
@@ -2845,12 +2797,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2868,14 +2820,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -2884,10 +2836,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O5" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P5" t="n">
         <v>4.3</v>
@@ -2907,13 +2859,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V5" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="6">
@@ -2932,12 +2884,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2955,14 +2907,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -2971,10 +2923,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N6" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O6" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -2994,13 +2946,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V6" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="7">
@@ -3019,12 +2971,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3042,14 +2994,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -3058,10 +3010,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O7" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P7" t="n">
         <v>4.3</v>
@@ -3081,13 +3033,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V7" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W7" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="8">
@@ -3106,22 +3058,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CRM, MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CRM: 2026-08-17 | MSFT: 2026-08-27</t>
+          <t>CRM: 2026-08-17</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3129,14 +3081,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
+          <t>CRM: +31.28% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.779711711691955</v>
+        <v>-2.702068946073233</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -3145,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="O8" t="n">
         <v>47.1</v>
@@ -3159,7 +3111,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>19.429</v>
@@ -3168,13 +3120,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>71.015</v>
+        <v>64.833</v>
       </c>
       <c r="V8" t="n">
-        <v>80.063</v>
+        <v>76.574</v>
       </c>
       <c r="W8" t="n">
-        <v>-17.984</v>
+        <v>-20.933</v>
       </c>
     </row>
     <row r="9">
@@ -3193,12 +3145,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3216,14 +3168,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -3232,10 +3184,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N9" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O9" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -3255,13 +3207,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V9" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="10">
@@ -3280,12 +3232,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3303,14 +3255,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -3319,10 +3271,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O10" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
@@ -3342,13 +3294,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V10" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W10" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="11">
@@ -3367,12 +3319,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3442,12 +3394,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3465,14 +3417,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
+          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-1.381618466137391</v>
       </c>
       <c r="K12" t="n">
-        <v>24.87307105054877</v>
+        <v>19.64112930541479</v>
       </c>
       <c r="L12" t="n">
         <v>10.56544794881541</v>
@@ -3504,13 +3456,13 @@
         <v>7.071</v>
       </c>
       <c r="U12" t="n">
-        <v>36.493</v>
+        <v>30.774</v>
       </c>
       <c r="V12" t="n">
-        <v>38.184</v>
+        <v>32.394</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-4.339</v>
       </c>
     </row>
     <row r="13">
@@ -3524,80 +3476,68 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>COP, OXY</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>19.02433828301018</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
-        </is>
-      </c>
+        <v>-5.737726850587677</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-0.759353416073727</v>
+        <v>-15.51355971349434</v>
       </c>
       <c r="K13" t="n">
-        <v>18.67914553579049</v>
+        <v>14.16765759127694</v>
       </c>
       <c r="L13" t="n">
-        <v>11.1266875</v>
+        <v>22.83624131316222</v>
       </c>
       <c r="M13" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>74.2</v>
+        <v>47.7</v>
       </c>
       <c r="O13" t="n">
-        <v>55</v>
+        <v>56.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>13.226</v>
+        <v>15.881</v>
       </c>
       <c r="T13" t="n">
-        <v>13.226</v>
+        <v>13.069</v>
       </c>
       <c r="U13" t="n">
-        <v>73.274</v>
+        <v>75.04900000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>76.53700000000001</v>
+        <v>98.842</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="14">
@@ -3611,80 +3551,68 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>COP, OXY</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>19.02433828301018</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
-        </is>
-      </c>
+        <v>-4.039576813106816</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-0.759353416073727</v>
+        <v>-15.51412294404569</v>
       </c>
       <c r="K14" t="n">
-        <v>18.67914553579049</v>
+        <v>14.16764711666048</v>
       </c>
       <c r="L14" t="n">
-        <v>11.1266875</v>
+        <v>22.8370162826819</v>
       </c>
       <c r="M14" t="n">
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>74.2</v>
+        <v>45.2</v>
       </c>
       <c r="O14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>13.226</v>
+        <v>15.882</v>
       </c>
       <c r="T14" t="n">
-        <v>13.226</v>
+        <v>12.892</v>
       </c>
       <c r="U14" t="n">
-        <v>73.274</v>
+        <v>56.587</v>
       </c>
       <c r="V14" t="n">
-        <v>76.53700000000001</v>
+        <v>77.873</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="16">
@@ -3829,22 +3757,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRM, MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CRM: 2026-08-17 | MSFT: 2026-08-27</t>
+          <t>CRM: 2026-08-17</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3852,14 +3780,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +37.18% / +40.48% / 0.00% | MSFT: -0.97% / +2.52% / -3.77%</t>
+          <t>CRM: +31.28% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.779711711691955</v>
+        <v>-2.702068946073233</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -3868,7 +3796,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="O18" t="n">
         <v>47.1</v>
@@ -3882,7 +3810,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>19.429</v>
@@ -3891,13 +3819,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>71.015</v>
+        <v>64.833</v>
       </c>
       <c r="V18" t="n">
-        <v>80.063</v>
+        <v>76.574</v>
       </c>
       <c r="W18" t="n">
-        <v>-17.984</v>
+        <v>-20.933</v>
       </c>
     </row>
     <row r="19">
@@ -3918,12 +3846,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3941,14 +3869,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MU: -0.02% / +0.00% / 0.00% | NVDA: +0.45% / +1.41% / 0.00%</t>
+          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.986162718867126</v>
+        <v>-2.957244675542336</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -3957,10 +3885,10 @@
         <v>72.22222222222221</v>
       </c>
       <c r="N19" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="O19" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -3980,13 +3908,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>28.879</v>
+        <v>30.26</v>
       </c>
       <c r="V19" t="n">
-        <v>15.285</v>
+        <v>16.52</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.92</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="20">
@@ -4007,12 +3935,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4030,14 +3958,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -2.92% / +0.00% / -3.25% | COP: +2.19% / +2.49% / -0.75%</t>
+          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.437760804543488</v>
+        <v>-5.723820999200758</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -4046,10 +3974,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="O20" t="n">
-        <v>58.2</v>
+        <v>57.1</v>
       </c>
       <c r="P20" t="n">
         <v>4.3</v>
@@ -4069,102 +3997,90 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>35.428</v>
+        <v>31.042</v>
       </c>
       <c r="V20" t="n">
-        <v>24.729</v>
+        <v>21.776</v>
       </c>
       <c r="W20" t="n">
-        <v>-4.821</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>COP, OXY</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>19.02433828301018</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
-        </is>
-      </c>
+        <v>11.64377880826557</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>-0.759353416073727</v>
+        <v>6.729894491660082</v>
       </c>
       <c r="K21" t="n">
-        <v>18.67914553579049</v>
+        <v>0.231855628775679</v>
       </c>
       <c r="L21" t="n">
-        <v>11.1266875</v>
+        <v>5.137942413230245</v>
       </c>
       <c r="M21" t="n">
-        <v>77.77777777777779</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>74.2</v>
+        <v>17.9</v>
       </c>
       <c r="O21" t="n">
-        <v>55</v>
+        <v>58.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>13.226</v>
+        <v>8.561</v>
       </c>
       <c r="T21" t="n">
-        <v>13.226</v>
+        <v>8.561</v>
       </c>
       <c r="U21" t="n">
-        <v>73.274</v>
+        <v>46.205</v>
       </c>
       <c r="V21" t="n">
-        <v>76.53700000000001</v>
+        <v>39.702</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-3.629</v>
       </c>
     </row>
     <row r="22">
@@ -4175,62 +4091,62 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M30|performans|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Ppuan|vidya_trend</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COP, OXY</t>
+          <t>COP, CRM</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>COP: 2026-09-11 | OXY: 2026-09-11</t>
+          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>19.02433828301018</v>
+        <v>5.926857774740779</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COP: +2.19% / +2.49% / -0.75% | OXY: +3.12% / +3.25% / -0.11%</t>
+          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.759353416073727</v>
+        <v>-1.381618466137391</v>
       </c>
       <c r="K22" t="n">
-        <v>18.67914553579049</v>
+        <v>19.64112930541479</v>
       </c>
       <c r="L22" t="n">
-        <v>11.1266875</v>
+        <v>10.56544794881541</v>
       </c>
       <c r="M22" t="n">
-        <v>77.77777777777779</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="N22" t="n">
-        <v>74.2</v>
+        <v>17.4</v>
       </c>
       <c r="O22" t="n">
-        <v>55</v>
+        <v>65.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4241,25 +4157,25 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>13.226</v>
+        <v>7.071</v>
       </c>
       <c r="T22" t="n">
-        <v>13.226</v>
+        <v>7.071</v>
       </c>
       <c r="U22" t="n">
-        <v>73.274</v>
+        <v>30.774</v>
       </c>
       <c r="V22" t="n">
-        <v>76.53700000000001</v>
+        <v>32.394</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-4.339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>LAST_3_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4269,45 +4185,45 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>11.64377880826557</v>
+        <v>-4.039576813106816</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>6.729894491660082</v>
+        <v>-15.51412294404569</v>
       </c>
       <c r="K23" t="n">
-        <v>0.231855628775679</v>
+        <v>14.16764711666048</v>
       </c>
       <c r="L23" t="n">
-        <v>5.137942413230245</v>
+        <v>22.8370162826819</v>
       </c>
       <c r="M23" t="n">
-        <v>38.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>17.9</v>
+        <v>45.2</v>
       </c>
       <c r="O23" t="n">
-        <v>58.3</v>
+        <v>56</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4318,19 +4234,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>8.561</v>
+        <v>15.882</v>
       </c>
       <c r="T23" t="n">
-        <v>8.561</v>
+        <v>12.892</v>
       </c>
       <c r="U23" t="n">
-        <v>46.205</v>
+        <v>56.587</v>
       </c>
       <c r="V23" t="n">
-        <v>39.702</v>
+        <v>77.873</v>
       </c>
       <c r="W23" t="n">
-        <v>-3.629</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="24">
@@ -4341,85 +4257,73 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>5.926857774740779</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>COP: +12.71% / +13.05% / 0.00% | CRM: +32.64% / +35.83% / -3.85%</t>
-        </is>
-      </c>
+        <v>-5.737726850587677</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>-1.381618466137391</v>
+        <v>-15.51355971349434</v>
       </c>
       <c r="K24" t="n">
-        <v>24.87307105054877</v>
+        <v>14.16765759127694</v>
       </c>
       <c r="L24" t="n">
-        <v>10.56544794881541</v>
+        <v>22.83624131316222</v>
       </c>
       <c r="M24" t="n">
-        <v>38.88888888888889</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>17.4</v>
+        <v>47.7</v>
       </c>
       <c r="O24" t="n">
-        <v>65.7</v>
+        <v>56.2</v>
       </c>
       <c r="P24" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>7.071</v>
+        <v>15.881</v>
       </c>
       <c r="T24" t="n">
-        <v>7.071</v>
+        <v>13.069</v>
       </c>
       <c r="U24" t="n">
-        <v>36.493</v>
+        <v>75.04900000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>38.184</v>
+        <v>98.842</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-5.859</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -756,14 +756,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +31.28% / +40.48% / 0.00%</t>
+          <t>CRM: +31.17% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.702068946073233</v>
+        <v>-3.047467294844641</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -795,13 +795,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>64.833</v>
+        <v>64.248</v>
       </c>
       <c r="V3" t="n">
-        <v>76.574</v>
+        <v>75.947</v>
       </c>
       <c r="W3" t="n">
-        <v>-20.933</v>
+        <v>-21.519</v>
       </c>
     </row>
     <row r="4">
@@ -843,14 +843,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -862,7 +862,7 @@
         <v>42.2</v>
       </c>
       <c r="O4" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -882,13 +882,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V4" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="5">
@@ -922,7 +922,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -930,14 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -946,10 +946,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O5" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P5" t="n">
         <v>4.3</v>
@@ -969,13 +969,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V5" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W5" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="6">
@@ -1017,14 +1017,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -1036,7 +1036,7 @@
         <v>42.2</v>
       </c>
       <c r="O6" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -1056,13 +1056,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V6" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="7">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -1120,10 +1120,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O7" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P7" t="n">
         <v>4.3</v>
@@ -1143,13 +1143,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V7" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W7" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="8">
@@ -1191,14 +1191,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +31.28% / +40.48% / 0.00%</t>
+          <t>CRM: +31.17% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.702068946073233</v>
+        <v>-3.047467294844641</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -1230,13 +1230,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>64.833</v>
+        <v>64.248</v>
       </c>
       <c r="V8" t="n">
-        <v>76.574</v>
+        <v>75.947</v>
       </c>
       <c r="W8" t="n">
-        <v>-20.933</v>
+        <v>-21.519</v>
       </c>
     </row>
     <row r="9">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -1297,7 +1297,7 @@
         <v>42.2</v>
       </c>
       <c r="O9" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -1317,13 +1317,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V9" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="10">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1365,14 +1365,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -1381,10 +1381,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O10" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
@@ -1404,13 +1404,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V10" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="11">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1512,67 +1512,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>5.926857774740779</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
-        </is>
-      </c>
+        <v>0.08861058164342239</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-1.381618466137391</v>
+        <v>-8.202644821914962</v>
       </c>
       <c r="K12" t="n">
-        <v>19.64112930541479</v>
+        <v>19.34320396880098</v>
       </c>
       <c r="L12" t="n">
-        <v>10.56544794881541</v>
+        <v>16.0458828125</v>
       </c>
       <c r="M12" t="n">
-        <v>38.88888888888889</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>17.4</v>
+        <v>26.8</v>
       </c>
       <c r="O12" t="n">
-        <v>65.7</v>
+        <v>53.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="T12" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="U12" t="n">
-        <v>30.774</v>
+        <v>87.17400000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>32.394</v>
+        <v>85.959</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.339</v>
+        <v>-2.387</v>
       </c>
     </row>
     <row r="13">
@@ -1890,14 +1878,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +31.28% / +40.48% / 0.00%</t>
+          <t>CRM: +31.17% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.702068946073233</v>
+        <v>-3.047467294844641</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -1929,13 +1917,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>64.833</v>
+        <v>64.248</v>
       </c>
       <c r="V18" t="n">
-        <v>76.574</v>
+        <v>75.947</v>
       </c>
       <c r="W18" t="n">
-        <v>-20.933</v>
+        <v>-21.519</v>
       </c>
     </row>
     <row r="19">
@@ -1979,14 +1967,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -1998,7 +1986,7 @@
         <v>42.2</v>
       </c>
       <c r="O19" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -2018,13 +2006,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V19" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="20">
@@ -2060,7 +2048,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2068,14 +2056,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -2084,10 +2072,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O20" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P20" t="n">
         <v>4.3</v>
@@ -2107,13 +2095,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V20" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W20" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="21">
@@ -2206,7 +2194,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2219,67 +2207,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5.926857774740779</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
-        </is>
-      </c>
+        <v>0.08861058164342239</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>-1.381618466137391</v>
+        <v>-8.202644821914962</v>
       </c>
       <c r="K22" t="n">
-        <v>19.64112930541479</v>
+        <v>19.34320396880098</v>
       </c>
       <c r="L22" t="n">
-        <v>10.56544794881541</v>
+        <v>16.0458828125</v>
       </c>
       <c r="M22" t="n">
-        <v>38.88888888888889</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N22" t="n">
-        <v>17.4</v>
+        <v>26.8</v>
       </c>
       <c r="O22" t="n">
-        <v>65.7</v>
+        <v>53.7</v>
       </c>
       <c r="P22" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="T22" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="U22" t="n">
-        <v>30.774</v>
+        <v>87.17400000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>32.394</v>
+        <v>85.959</v>
       </c>
       <c r="W22" t="n">
-        <v>-4.339</v>
+        <v>-2.387</v>
       </c>
     </row>
     <row r="23">
@@ -2646,14 +2622,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRM: +31.28% / +40.48% / 0.00%</t>
+          <t>CRM: +31.17% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.702068946073233</v>
+        <v>-3.047467294844641</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -2685,13 +2661,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>64.833</v>
+        <v>64.248</v>
       </c>
       <c r="V3" t="n">
-        <v>76.574</v>
+        <v>75.947</v>
       </c>
       <c r="W3" t="n">
-        <v>-20.933</v>
+        <v>-21.519</v>
       </c>
     </row>
     <row r="4">
@@ -2733,14 +2709,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -2752,7 +2728,7 @@
         <v>42.2</v>
       </c>
       <c r="O4" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -2772,13 +2748,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V4" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="5">
@@ -2812,7 +2788,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2820,14 +2796,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -2836,10 +2812,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O5" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P5" t="n">
         <v>4.3</v>
@@ -2859,13 +2835,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V5" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W5" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="6">
@@ -2907,14 +2883,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -2926,7 +2902,7 @@
         <v>42.2</v>
       </c>
       <c r="O6" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
@@ -2946,13 +2922,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V6" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="7">
@@ -2986,7 +2962,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2994,14 +2970,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -3010,10 +2986,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O7" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P7" t="n">
         <v>4.3</v>
@@ -3033,13 +3009,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V7" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W7" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="8">
@@ -3081,14 +3057,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CRM: +31.28% / +40.48% / 0.00%</t>
+          <t>CRM: +31.17% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.702068946073233</v>
+        <v>-3.047467294844641</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -3120,13 +3096,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>64.833</v>
+        <v>64.248</v>
       </c>
       <c r="V8" t="n">
-        <v>76.574</v>
+        <v>75.947</v>
       </c>
       <c r="W8" t="n">
-        <v>-20.933</v>
+        <v>-21.519</v>
       </c>
     </row>
     <row r="9">
@@ -3168,14 +3144,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -3187,7 +3163,7 @@
         <v>42.2</v>
       </c>
       <c r="O9" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
@@ -3207,13 +3183,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V9" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="10">
@@ -3247,7 +3223,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3255,14 +3231,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -3271,10 +3247,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O10" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
@@ -3294,13 +3270,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V10" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W10" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="11">
@@ -3389,7 +3365,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3402,67 +3378,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>5.926857774740779</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
-        </is>
-      </c>
+        <v>0.08861058164342239</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>-1.381618466137391</v>
+        <v>-8.202644821914962</v>
       </c>
       <c r="K12" t="n">
-        <v>19.64112930541479</v>
+        <v>19.34320396880098</v>
       </c>
       <c r="L12" t="n">
-        <v>10.56544794881541</v>
+        <v>16.0458828125</v>
       </c>
       <c r="M12" t="n">
-        <v>38.88888888888889</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N12" t="n">
-        <v>17.4</v>
+        <v>26.8</v>
       </c>
       <c r="O12" t="n">
-        <v>65.7</v>
+        <v>53.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="T12" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="U12" t="n">
-        <v>30.774</v>
+        <v>87.17400000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>32.394</v>
+        <v>85.959</v>
       </c>
       <c r="W12" t="n">
-        <v>-4.339</v>
+        <v>-2.387</v>
       </c>
     </row>
     <row r="13">
@@ -3780,14 +3744,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CRM: +31.28% / +40.48% / 0.00%</t>
+          <t>CRM: +31.17% / +40.48% / 0.00%</t>
         </is>
       </c>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.702068946073233</v>
+        <v>-3.047467294844641</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -3819,13 +3783,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>64.833</v>
+        <v>64.248</v>
       </c>
       <c r="V18" t="n">
-        <v>76.574</v>
+        <v>75.947</v>
       </c>
       <c r="W18" t="n">
-        <v>-20.933</v>
+        <v>-21.519</v>
       </c>
     </row>
     <row r="19">
@@ -3869,14 +3833,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MU: +0.12% / +1.25% / -0.53% | NVDA: +2.31% / +2.75% / 0.00%</t>
+          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.957244675542336</v>
+        <v>-3.513287140780275</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -3888,7 +3852,7 @@
         <v>42.2</v>
       </c>
       <c r="O19" t="n">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
@@ -3908,13 +3872,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>30.26</v>
+        <v>29.514</v>
       </c>
       <c r="V19" t="n">
-        <v>16.52</v>
+        <v>15.852</v>
       </c>
       <c r="W19" t="n">
-        <v>-5.539</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="20">
@@ -3950,7 +3914,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-11 | COP: 2026-09-11</t>
+          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3958,14 +3922,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AMZN: -3.49% / +0.00% / -3.93% | COP: -1.97% / +3.11% / -2.93%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.723820999200758</v>
+        <v>-6.754315303152502</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -3974,10 +3938,10 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="O20" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="P20" t="n">
         <v>4.3</v>
@@ -3997,13 +3961,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>31.042</v>
+        <v>29.609</v>
       </c>
       <c r="V20" t="n">
-        <v>21.776</v>
+        <v>20.445</v>
       </c>
       <c r="W20" t="n">
-        <v>-7.956</v>
+        <v>-9.388</v>
       </c>
     </row>
     <row r="21">
@@ -4096,7 +4060,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4109,67 +4073,55 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>COP, CRM</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>COP: 2026-08-13 | CRM: 2026-08-10</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5.926857774740779</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>COP: +8.13% / +13.73% / 0.00% | CRM: +26.94% / +35.83% / -3.85%</t>
-        </is>
-      </c>
+        <v>0.08861058164342239</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>-1.381618466137391</v>
+        <v>-8.202644821914962</v>
       </c>
       <c r="K22" t="n">
-        <v>19.64112930541479</v>
+        <v>19.34320396880098</v>
       </c>
       <c r="L22" t="n">
-        <v>10.56544794881541</v>
+        <v>16.0458828125</v>
       </c>
       <c r="M22" t="n">
-        <v>38.88888888888889</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="N22" t="n">
-        <v>17.4</v>
+        <v>26.8</v>
       </c>
       <c r="O22" t="n">
-        <v>65.7</v>
+        <v>53.7</v>
       </c>
       <c r="P22" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="T22" t="n">
-        <v>7.071</v>
+        <v>20.787</v>
       </c>
       <c r="U22" t="n">
-        <v>30.774</v>
+        <v>87.17400000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>32.394</v>
+        <v>85.959</v>
       </c>
       <c r="W22" t="n">
-        <v>-4.339</v>
+        <v>-2.387</v>
       </c>
     </row>
     <row r="23">

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -574,9 +574,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -733,37 +733,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CRM: 2026-08-17</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>49.35390788200862</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CRM: +31.17% / +40.48% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.047467294844641</v>
+        <v>-3.869530333751614</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -772,7 +760,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="O3" t="n">
         <v>47.1</v>
@@ -782,11 +770,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>19.429</v>
@@ -795,13 +783,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>64.248</v>
+        <v>61.479</v>
       </c>
       <c r="V3" t="n">
-        <v>75.947</v>
+        <v>74.455</v>
       </c>
       <c r="W3" t="n">
-        <v>-21.519</v>
+        <v>-22.718</v>
       </c>
     </row>
     <row r="4">
@@ -820,37 +808,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -862,18 +838,18 @@
         <v>42.2</v>
       </c>
       <c r="O4" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>7.489</v>
@@ -882,13 +858,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V4" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="5">
@@ -907,37 +883,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -946,21 +910,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O5" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P5" t="n">
         <v>4.3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>9.178000000000001</v>
@@ -969,13 +933,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V5" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W5" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="6">
@@ -994,37 +958,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -1036,18 +988,18 @@
         <v>42.2</v>
       </c>
       <c r="O6" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>7.489</v>
@@ -1056,13 +1008,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V6" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="7">
@@ -1081,37 +1033,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -1120,21 +1060,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O7" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P7" t="n">
         <v>4.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>9.178000000000001</v>
@@ -1143,13 +1083,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V7" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="8">
@@ -1168,37 +1108,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CRM: 2026-08-17</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>49.35390788200862</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CRM: +31.17% / +40.48% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.047467294844641</v>
+        <v>-3.869530333751614</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -1207,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="O8" t="n">
         <v>47.1</v>
@@ -1217,11 +1145,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>19.429</v>
@@ -1230,13 +1158,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>64.248</v>
+        <v>61.479</v>
       </c>
       <c r="V8" t="n">
-        <v>75.947</v>
+        <v>74.455</v>
       </c>
       <c r="W8" t="n">
-        <v>-21.519</v>
+        <v>-22.718</v>
       </c>
     </row>
     <row r="9">
@@ -1255,37 +1183,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -1297,18 +1213,18 @@
         <v>42.2</v>
       </c>
       <c r="O9" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>7.489</v>
@@ -1317,13 +1233,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V9" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="10">
@@ -1342,37 +1258,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -1381,21 +1285,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O10" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>9.178000000000001</v>
@@ -1404,13 +1308,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V10" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="11">
@@ -1429,12 +1333,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1479,7 +1383,7 @@
         <v>8.561</v>
       </c>
       <c r="U11" t="n">
-        <v>46.205</v>
+        <v>46.219</v>
       </c>
       <c r="V11" t="n">
         <v>39.702</v>
@@ -1504,12 +1408,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1554,13 +1458,13 @@
         <v>20.787</v>
       </c>
       <c r="U12" t="n">
-        <v>87.17400000000001</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>85.959</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.387</v>
+        <v>-2.378</v>
       </c>
     </row>
     <row r="13">
@@ -1579,12 +1483,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1606,7 +1510,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="O13" t="n">
         <v>56.2</v>
@@ -1629,13 +1533,13 @@
         <v>13.069</v>
       </c>
       <c r="U13" t="n">
-        <v>75.04900000000001</v>
+        <v>74.419</v>
       </c>
       <c r="V13" t="n">
         <v>98.842</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.859</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="14">
@@ -1654,12 +1558,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1681,7 +1585,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="O14" t="n">
         <v>56</v>
@@ -1704,13 +1608,13 @@
         <v>12.892</v>
       </c>
       <c r="U14" t="n">
-        <v>56.587</v>
+        <v>56.024</v>
       </c>
       <c r="V14" t="n">
         <v>77.873</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.241</v>
+        <v>-5.222</v>
       </c>
     </row>
     <row r="16">
@@ -1855,37 +1759,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CRM: 2026-08-17</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>49.35390788200862</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CRM: +31.17% / +40.48% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.047467294844641</v>
+        <v>-3.869530333751614</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -1894,7 +1786,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="O18" t="n">
         <v>47.1</v>
@@ -1904,11 +1796,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>19.429</v>
@@ -1917,13 +1809,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>64.248</v>
+        <v>61.479</v>
       </c>
       <c r="V18" t="n">
-        <v>75.947</v>
+        <v>74.455</v>
       </c>
       <c r="W18" t="n">
-        <v>-21.519</v>
+        <v>-22.718</v>
       </c>
     </row>
     <row r="19">
@@ -1944,37 +1836,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -1986,18 +1866,18 @@
         <v>42.2</v>
       </c>
       <c r="O19" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>7.489</v>
@@ -2006,13 +1886,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V19" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="20">
@@ -2033,37 +1913,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -2072,21 +1940,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O20" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P20" t="n">
         <v>4.3</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>9.178000000000001</v>
@@ -2095,13 +1963,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V20" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W20" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="21">
@@ -2122,12 +1990,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2172,7 +2040,7 @@
         <v>8.561</v>
       </c>
       <c r="U21" t="n">
-        <v>46.205</v>
+        <v>46.219</v>
       </c>
       <c r="V21" t="n">
         <v>39.702</v>
@@ -2199,12 +2067,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2249,13 +2117,13 @@
         <v>20.787</v>
       </c>
       <c r="U22" t="n">
-        <v>87.17400000000001</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="V22" t="n">
         <v>85.959</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.387</v>
+        <v>-2.378</v>
       </c>
     </row>
     <row r="23">
@@ -2276,12 +2144,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -2303,7 +2171,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="O23" t="n">
         <v>56</v>
@@ -2326,13 +2194,13 @@
         <v>12.892</v>
       </c>
       <c r="U23" t="n">
-        <v>56.587</v>
+        <v>56.024</v>
       </c>
       <c r="V23" t="n">
         <v>77.873</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.241</v>
+        <v>-5.222</v>
       </c>
     </row>
     <row r="24">
@@ -2353,12 +2221,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2380,7 +2248,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="O24" t="n">
         <v>56.2</v>
@@ -2403,13 +2271,13 @@
         <v>13.069</v>
       </c>
       <c r="U24" t="n">
-        <v>75.04900000000001</v>
+        <v>74.419</v>
       </c>
       <c r="V24" t="n">
         <v>98.842</v>
       </c>
       <c r="W24" t="n">
-        <v>-5.859</v>
+        <v>-5.838</v>
       </c>
     </row>
   </sheetData>
@@ -2440,9 +2308,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -2599,37 +2467,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CRM: 2026-08-17</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>49.35390788200862</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CRM: +31.17% / +40.48% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.047467294844641</v>
+        <v>-3.869530333751614</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -2638,7 +2494,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="O3" t="n">
         <v>47.1</v>
@@ -2648,11 +2504,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>19.429</v>
@@ -2661,13 +2517,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>64.248</v>
+        <v>61.479</v>
       </c>
       <c r="V3" t="n">
-        <v>75.947</v>
+        <v>74.455</v>
       </c>
       <c r="W3" t="n">
-        <v>-21.519</v>
+        <v>-22.718</v>
       </c>
     </row>
     <row r="4">
@@ -2686,37 +2542,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -2728,18 +2572,18 @@
         <v>42.2</v>
       </c>
       <c r="O4" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>7.489</v>
@@ -2748,13 +2592,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V4" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W4" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="5">
@@ -2773,37 +2617,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -2812,21 +2644,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O5" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P5" t="n">
         <v>4.3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>9.178000000000001</v>
@@ -2835,13 +2667,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V5" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W5" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="6">
@@ -2860,37 +2692,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -2902,18 +2722,18 @@
         <v>42.2</v>
       </c>
       <c r="O6" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>7.489</v>
@@ -2922,13 +2742,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V6" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W6" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="7">
@@ -2947,37 +2767,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -2986,21 +2794,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O7" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P7" t="n">
         <v>4.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>9.178000000000001</v>
@@ -3009,13 +2817,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V7" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="8">
@@ -3034,37 +2842,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CRM: 2026-08-17</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>49.35390788200862</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CRM: +31.17% / +40.48% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.047467294844641</v>
+        <v>-3.869530333751614</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -3073,7 +2869,7 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="O8" t="n">
         <v>47.1</v>
@@ -3083,11 +2879,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>19.429</v>
@@ -3096,13 +2892,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>64.248</v>
+        <v>61.479</v>
       </c>
       <c r="V8" t="n">
-        <v>75.947</v>
+        <v>74.455</v>
       </c>
       <c r="W8" t="n">
-        <v>-21.519</v>
+        <v>-22.718</v>
       </c>
     </row>
     <row r="9">
@@ -3121,37 +2917,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -3163,18 +2947,18 @@
         <v>42.2</v>
       </c>
       <c r="O9" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>7.489</v>
@@ -3183,13 +2967,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V9" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W9" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="10">
@@ -3208,37 +2992,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -3247,21 +3019,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O10" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P10" t="n">
         <v>4.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>9.178000000000001</v>
@@ -3270,13 +3042,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V10" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W10" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="11">
@@ -3295,12 +3067,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3345,7 +3117,7 @@
         <v>8.561</v>
       </c>
       <c r="U11" t="n">
-        <v>46.205</v>
+        <v>46.219</v>
       </c>
       <c r="V11" t="n">
         <v>39.702</v>
@@ -3370,12 +3142,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3420,13 +3192,13 @@
         <v>20.787</v>
       </c>
       <c r="U12" t="n">
-        <v>87.17400000000001</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>85.959</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.387</v>
+        <v>-2.378</v>
       </c>
     </row>
     <row r="13">
@@ -3445,12 +3217,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3472,7 +3244,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N13" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="O13" t="n">
         <v>56.2</v>
@@ -3495,13 +3267,13 @@
         <v>13.069</v>
       </c>
       <c r="U13" t="n">
-        <v>75.04900000000001</v>
+        <v>74.419</v>
       </c>
       <c r="V13" t="n">
         <v>98.842</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.859</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="14">
@@ -3520,12 +3292,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3547,7 +3319,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N14" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="O14" t="n">
         <v>56</v>
@@ -3570,13 +3342,13 @@
         <v>12.892</v>
       </c>
       <c r="U14" t="n">
-        <v>56.587</v>
+        <v>56.024</v>
       </c>
       <c r="V14" t="n">
         <v>77.873</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.241</v>
+        <v>-5.222</v>
       </c>
     </row>
     <row r="16">
@@ -3721,37 +3493,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CRM: 2026-08-17</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>49.35390788200862</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CRM: +31.17% / +40.48% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.047467294844641</v>
+        <v>-3.869530333751614</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -3760,7 +3520,7 @@
         <v>100</v>
       </c>
       <c r="N18" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="O18" t="n">
         <v>47.1</v>
@@ -3770,11 +3530,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>19.429</v>
@@ -3783,13 +3543,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>64.248</v>
+        <v>61.479</v>
       </c>
       <c r="V18" t="n">
-        <v>75.947</v>
+        <v>74.455</v>
       </c>
       <c r="W18" t="n">
-        <v>-21.519</v>
+        <v>-22.718</v>
       </c>
     </row>
     <row r="19">
@@ -3810,37 +3570,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MU, NVDA</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MU: 2026-09-15 | NVDA: 2026-09-14</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>46.89202291173533</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>MU: -0.13% / +1.47% / -1.07% | NVDA: +1.37% / +2.75% / 0.00%</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.513287140780275</v>
+        <v>0.1334174702701807</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -3852,18 +3600,18 @@
         <v>42.2</v>
       </c>
       <c r="O19" t="n">
-        <v>61.2</v>
+        <v>62.4</v>
       </c>
       <c r="P19" t="n">
         <v>2.3</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>7.489</v>
@@ -3872,13 +3620,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>29.514</v>
+        <v>34.422</v>
       </c>
       <c r="V19" t="n">
-        <v>15.852</v>
+        <v>20.231</v>
       </c>
       <c r="W19" t="n">
-        <v>-6.285</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="20">
@@ -3899,37 +3647,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AMZN, COP</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AMZN: 2026-09-16 | COP: 2026-09-11</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>44.24447097072779</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | COP: -3.52% / +3.11% / -3.62%</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.754315303152502</v>
+        <v>-6.18401224164058</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -3938,21 +3674,21 @@
         <v>83.33333333333334</v>
       </c>
       <c r="N20" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="O20" t="n">
-        <v>56.6</v>
+        <v>57.6</v>
       </c>
       <c r="P20" t="n">
         <v>4.3</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ACIK</t>
+          <t>NAKIT_SINYAL_YOK</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>9.178000000000001</v>
@@ -3961,13 +3697,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>29.609</v>
+        <v>30.916</v>
       </c>
       <c r="V20" t="n">
-        <v>20.445</v>
+        <v>21.182</v>
       </c>
       <c r="W20" t="n">
-        <v>-9.388</v>
+        <v>-8.629</v>
       </c>
     </row>
     <row r="21">
@@ -3988,12 +3724,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4038,7 +3774,7 @@
         <v>8.561</v>
       </c>
       <c r="U21" t="n">
-        <v>46.205</v>
+        <v>46.219</v>
       </c>
       <c r="V21" t="n">
         <v>39.702</v>
@@ -4065,12 +3801,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4115,13 +3851,13 @@
         <v>20.787</v>
       </c>
       <c r="U22" t="n">
-        <v>87.17400000000001</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="V22" t="n">
         <v>85.959</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.387</v>
+        <v>-2.378</v>
       </c>
     </row>
     <row r="23">
@@ -4142,12 +3878,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4169,7 +3905,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N23" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="O23" t="n">
         <v>56</v>
@@ -4192,13 +3928,13 @@
         <v>12.892</v>
       </c>
       <c r="U23" t="n">
-        <v>56.587</v>
+        <v>56.024</v>
       </c>
       <c r="V23" t="n">
         <v>77.873</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.241</v>
+        <v>-5.222</v>
       </c>
     </row>
     <row r="24">
@@ -4219,12 +3955,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4246,7 +3982,7 @@
         <v>77.77777777777779</v>
       </c>
       <c r="N24" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="O24" t="n">
         <v>56.2</v>
@@ -4269,13 +4005,13 @@
         <v>13.069</v>
       </c>
       <c r="U24" t="n">
-        <v>75.04900000000001</v>
+        <v>74.419</v>
       </c>
       <c r="V24" t="n">
         <v>98.842</v>
       </c>
       <c r="W24" t="n">
-        <v>-5.859</v>
+        <v>-5.838</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -751,7 +751,7 @@
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.869530333751614</v>
+        <v>-3.915826539070666</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -783,13 +783,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>61.479</v>
+        <v>61.402</v>
       </c>
       <c r="V3" t="n">
-        <v>74.455</v>
+        <v>74.371</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.718</v>
+        <v>-22.795</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +826,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -858,13 +858,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V4" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
@@ -901,7 +901,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -933,13 +933,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V5" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W5" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -976,7 +976,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -1008,13 +1008,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V6" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -1051,7 +1051,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -1083,13 +1083,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V7" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W7" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1126,7 +1126,7 @@
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.869530333751614</v>
+        <v>-3.915826539070666</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -1158,13 +1158,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>61.479</v>
+        <v>61.402</v>
       </c>
       <c r="V8" t="n">
-        <v>74.455</v>
+        <v>74.371</v>
       </c>
       <c r="W8" t="n">
-        <v>-22.718</v>
+        <v>-22.795</v>
       </c>
     </row>
     <row r="9">
@@ -1201,7 +1201,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -1233,13 +1233,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V9" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1276,7 +1276,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -1308,13 +1308,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V10" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1777,7 +1777,7 @@
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.869530333751614</v>
+        <v>-3.915826539070666</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -1809,13 +1809,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>61.479</v>
+        <v>61.402</v>
       </c>
       <c r="V18" t="n">
-        <v>74.455</v>
+        <v>74.371</v>
       </c>
       <c r="W18" t="n">
-        <v>-22.718</v>
+        <v>-22.795</v>
       </c>
     </row>
     <row r="19">
@@ -1854,7 +1854,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -1886,13 +1886,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V19" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -1931,7 +1931,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -1963,13 +1963,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V20" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2485,7 +2485,7 @@
         <v>14.53607138314319</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.869530333751614</v>
+        <v>-3.915826539070666</v>
       </c>
       <c r="L3" t="n">
         <v>16.46690178496608</v>
@@ -2517,13 +2517,13 @@
         <v>19.429</v>
       </c>
       <c r="U3" t="n">
-        <v>61.479</v>
+        <v>61.402</v>
       </c>
       <c r="V3" t="n">
-        <v>74.455</v>
+        <v>74.371</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.718</v>
+        <v>-22.795</v>
       </c>
     </row>
     <row r="4">
@@ -2560,7 +2560,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L4" t="n">
         <v>8.076882947230402</v>
@@ -2592,13 +2592,13 @@
         <v>7.489</v>
       </c>
       <c r="U4" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V4" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
@@ -2635,7 +2635,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L5" t="n">
         <v>8.338915824512183</v>
@@ -2667,13 +2667,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V5" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W5" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2710,7 +2710,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L6" t="n">
         <v>8.076882947230402</v>
@@ -2742,13 +2742,13 @@
         <v>7.489</v>
       </c>
       <c r="U6" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V6" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -2785,7 +2785,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L7" t="n">
         <v>8.338915824512183</v>
@@ -2817,13 +2817,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V7" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W7" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2860,7 +2860,7 @@
         <v>14.53607138314319</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.869530333751614</v>
+        <v>-3.915826539070666</v>
       </c>
       <c r="L8" t="n">
         <v>16.46690178496608</v>
@@ -2892,13 +2892,13 @@
         <v>19.429</v>
       </c>
       <c r="U8" t="n">
-        <v>61.479</v>
+        <v>61.402</v>
       </c>
       <c r="V8" t="n">
-        <v>74.455</v>
+        <v>74.371</v>
       </c>
       <c r="W8" t="n">
-        <v>-22.718</v>
+        <v>-22.795</v>
       </c>
     </row>
     <row r="9">
@@ -2935,7 +2935,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L9" t="n">
         <v>8.076882947230402</v>
@@ -2967,13 +2967,13 @@
         <v>7.489</v>
       </c>
       <c r="U9" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V9" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -3010,7 +3010,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L10" t="n">
         <v>8.338915824512183</v>
@@ -3042,13 +3042,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V10" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3511,7 +3511,7 @@
         <v>14.53607138314319</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.869530333751614</v>
+        <v>-3.915826539070666</v>
       </c>
       <c r="L18" t="n">
         <v>16.46690178496608</v>
@@ -3543,13 +3543,13 @@
         <v>19.429</v>
       </c>
       <c r="U18" t="n">
-        <v>61.479</v>
+        <v>61.402</v>
       </c>
       <c r="V18" t="n">
-        <v>74.455</v>
+        <v>74.371</v>
       </c>
       <c r="W18" t="n">
-        <v>-22.718</v>
+        <v>-22.795</v>
       </c>
     </row>
     <row r="19">
@@ -3588,7 +3588,7 @@
         <v>20.23942766288032</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1334174702701807</v>
+        <v>0.3272617918051557</v>
       </c>
       <c r="L19" t="n">
         <v>8.076882947230402</v>
@@ -3620,13 +3620,13 @@
         <v>7.489</v>
       </c>
       <c r="U19" t="n">
-        <v>34.422</v>
+        <v>34.682</v>
       </c>
       <c r="V19" t="n">
-        <v>20.231</v>
+        <v>20.464</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
@@ -3665,7 +3665,7 @@
         <v>16.3270873608562</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.18401224164058</v>
+        <v>-6.202916842117645</v>
       </c>
       <c r="L20" t="n">
         <v>8.338915824512183</v>
@@ -3697,13 +3697,13 @@
         <v>9.178000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>30.916</v>
+        <v>30.889</v>
       </c>
       <c r="V20" t="n">
-        <v>21.182</v>
+        <v>21.157</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.629</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="21">

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W24" headerRowCount="1">
-  <autoFilter ref="A17:W24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ATL_1_2" displayName="ATL_1_2" ref="A17:W28" headerRowCount="1">
+  <autoFilter ref="A17:W28"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -245,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W24" headerRowCount="1">
-  <autoFilter ref="A17:W24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ATL_2_2" displayName="ATL_2_2" ref="A17:W28" headerRowCount="1">
+  <autoFilter ref="A17:W28"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Grup"/>
     <tableColumn id="2" name="Sira"/>
@@ -565,18 +565,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -744,29 +744,29 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>49.35390788200862</v>
+        <v>50.31783953782316</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>14.53607138314319</v>
+        <v>10.77487934152495</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.915826539070666</v>
+        <v>5.194089911712285</v>
       </c>
       <c r="L3" t="n">
-        <v>16.46690178496608</v>
+        <v>19.33725726507755</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="O3" t="n">
-        <v>47.1</v>
+        <v>51.8</v>
       </c>
       <c r="P3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -777,19 +777,19 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="T3" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>61.402</v>
+        <v>168.209</v>
       </c>
       <c r="V3" t="n">
-        <v>74.371</v>
+        <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.795</v>
+        <v>-23.133</v>
       </c>
     </row>
     <row r="4">
@@ -803,7 +803,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -819,26 +819,26 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>46.89202291173533</v>
+        <v>38.94248592369556</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>20.23942766288032</v>
+        <v>15.08563954368505</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3272617918051557</v>
+        <v>-7.289275987144639</v>
       </c>
       <c r="L4" t="n">
-        <v>8.076882947230402</v>
+        <v>12.5804569568174</v>
       </c>
       <c r="M4" t="n">
-        <v>72.22222222222221</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>42.2</v>
+        <v>76.5</v>
       </c>
       <c r="O4" t="n">
-        <v>62.4</v>
+        <v>48.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -852,19 +852,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>7.489</v>
+        <v>12.325</v>
       </c>
       <c r="T4" t="n">
-        <v>7.489</v>
+        <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>34.682</v>
+        <v>78.52</v>
       </c>
       <c r="V4" t="n">
-        <v>20.464</v>
+        <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.13</v>
+        <v>-23.493</v>
       </c>
     </row>
     <row r="5">
@@ -878,7 +878,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -894,29 +894,29 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>44.24447097072779</v>
+        <v>31.10445507363087</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>16.3270873608562</v>
+        <v>2.246452219851824</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.202916842117645</v>
+        <v>4.590130482453136</v>
       </c>
       <c r="L5" t="n">
-        <v>8.338915824512183</v>
+        <v>17.92592565753429</v>
       </c>
       <c r="M5" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>49.1</v>
+        <v>60.5</v>
       </c>
       <c r="O5" t="n">
-        <v>57.6</v>
+        <v>54.5</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -927,19 +927,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>9.178000000000001</v>
+        <v>15.835</v>
       </c>
       <c r="T5" t="n">
-        <v>9.178000000000001</v>
+        <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>30.889</v>
+        <v>130.51</v>
       </c>
       <c r="V5" t="n">
-        <v>21.157</v>
+        <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-8.656000000000001</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="6">
@@ -953,7 +953,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -969,29 +969,29 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>46.89202291173533</v>
+        <v>46.94985892607355</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>20.23942766288032</v>
+        <v>22.59150134949037</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3272617918051557</v>
+        <v>-1.195399439619516</v>
       </c>
       <c r="L6" t="n">
-        <v>8.076882947230402</v>
+        <v>14.54467229027953</v>
       </c>
       <c r="M6" t="n">
-        <v>72.22222222222221</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>42.2</v>
+        <v>148</v>
       </c>
       <c r="O6" t="n">
-        <v>62.4</v>
+        <v>53.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1002,19 +1002,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="T6" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>34.682</v>
+        <v>84.146</v>
       </c>
       <c r="V6" t="n">
-        <v>20.464</v>
+        <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.13</v>
+        <v>-13.132</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1044,29 +1044,29 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>44.24447097072779</v>
+        <v>38.94248592369556</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>16.3270873608562</v>
+        <v>15.08563954368505</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.202916842117645</v>
+        <v>-7.289275987144639</v>
       </c>
       <c r="L7" t="n">
-        <v>8.338915824512183</v>
+        <v>12.5804569568174</v>
       </c>
       <c r="M7" t="n">
-        <v>83.33333333333334</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>49.1</v>
+        <v>76.5</v>
       </c>
       <c r="O7" t="n">
-        <v>57.6</v>
+        <v>48.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>9.178000000000001</v>
+        <v>12.325</v>
       </c>
       <c r="T7" t="n">
-        <v>9.178000000000001</v>
+        <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>30.889</v>
+        <v>78.52</v>
       </c>
       <c r="V7" t="n">
-        <v>21.157</v>
+        <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-8.656000000000001</v>
+        <v>-23.493</v>
       </c>
     </row>
     <row r="8">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1116,55 +1116,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MRVL, MU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>49.35390788200862</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>26.20489633670095</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>14.53607138314319</v>
+        <v>9.984984890543625</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.915826539070666</v>
+        <v>6.752234869836449</v>
       </c>
       <c r="L8" t="n">
-        <v>16.46690178496608</v>
+        <v>18.40557500086005</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.3</v>
+        <v>164.5</v>
       </c>
       <c r="O8" t="n">
-        <v>47.1</v>
+        <v>51.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>19.429</v>
+        <v>23.406</v>
       </c>
       <c r="T8" t="n">
-        <v>19.429</v>
+        <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>61.402</v>
+        <v>24.858</v>
       </c>
       <c r="V8" t="n">
-        <v>74.371</v>
+        <v>19.426</v>
       </c>
       <c r="W8" t="n">
-        <v>-22.795</v>
+        <v>-11.181</v>
       </c>
     </row>
     <row r="9">
@@ -1178,7 +1190,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|hacim_kirilim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1194,29 +1206,29 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>46.89202291173533</v>
+        <v>20.20832547812279</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>20.23942766288032</v>
+        <v>8.328099283309044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3272617918051557</v>
+        <v>-0.3873406760593223</v>
       </c>
       <c r="L9" t="n">
-        <v>8.076882947230402</v>
+        <v>4.876696273694236</v>
       </c>
       <c r="M9" t="n">
-        <v>72.22222222222221</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="O9" t="n">
-        <v>62.4</v>
+        <v>45.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1227,19 +1239,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>7.489</v>
+        <v>4.651</v>
       </c>
       <c r="T9" t="n">
-        <v>7.489</v>
+        <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>34.682</v>
+        <v>36.485</v>
       </c>
       <c r="V9" t="n">
-        <v>20.464</v>
+        <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.13</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="10">
@@ -1253,7 +1265,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S5|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1269,29 +1281,29 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>44.24447097072779</v>
+        <v>46.50482418007029</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>16.3270873608562</v>
+        <v>22.22039417483554</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.202916842117645</v>
+        <v>-1.195399439619493</v>
       </c>
       <c r="L10" t="n">
-        <v>8.338915824512183</v>
+        <v>13.82158293080772</v>
       </c>
       <c r="M10" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>49.1</v>
+        <v>147</v>
       </c>
       <c r="O10" t="n">
-        <v>57.6</v>
+        <v>53.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1302,19 +1314,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="T10" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>30.889</v>
+        <v>81.583</v>
       </c>
       <c r="V10" t="n">
-        <v>21.157</v>
+        <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.656000000000001</v>
+        <v>-12.949</v>
       </c>
     </row>
     <row r="11">
@@ -1328,7 +1340,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1341,55 +1353,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>APH, COP</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>11.64377880826557</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>25.00234807668962</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J11" t="n">
-        <v>6.729894491660082</v>
+        <v>7.003544895075797</v>
       </c>
       <c r="K11" t="n">
-        <v>0.231855628775679</v>
+        <v>0.42099904130386</v>
       </c>
       <c r="L11" t="n">
-        <v>5.137942413230245</v>
+        <v>3.457636701004341</v>
       </c>
       <c r="M11" t="n">
-        <v>38.88888888888889</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>17.9</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>58.3</v>
+        <v>63.6</v>
       </c>
       <c r="P11" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>8.561</v>
+        <v>8.563000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>8.561</v>
+        <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>46.219</v>
+        <v>49.157</v>
       </c>
       <c r="V11" t="n">
-        <v>39.702</v>
+        <v>49.157</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.629</v>
+        <v>-11.175</v>
       </c>
     </row>
     <row r="12">
@@ -1403,7 +1427,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1416,55 +1440,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>0.08861058164342239</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>-8.202644821914962</v>
+        <v>-2.485427176837574</v>
       </c>
       <c r="K12" t="n">
-        <v>19.34320396880098</v>
+        <v>31.11411326152826</v>
       </c>
       <c r="L12" t="n">
-        <v>16.0458828125</v>
+        <v>7.879921591535</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666666</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N12" t="n">
-        <v>26.8</v>
+        <v>14.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53.7</v>
+        <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>20.787</v>
+        <v>7.264</v>
       </c>
       <c r="T12" t="n">
-        <v>20.787</v>
+        <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>86.48399999999999</v>
+        <v>86.517</v>
       </c>
       <c r="V12" t="n">
-        <v>85.959</v>
+        <v>86.517</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.378</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="13">
@@ -1478,7 +1514,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1491,55 +1527,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>-5.737726850587677</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-15.51355971349434</v>
+        <v>-2.485427176837574</v>
       </c>
       <c r="K13" t="n">
-        <v>14.16765759127694</v>
+        <v>31.11411326152826</v>
       </c>
       <c r="L13" t="n">
-        <v>22.83624131316222</v>
+        <v>7.879921591535</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N13" t="n">
-        <v>47.6</v>
+        <v>14.5</v>
       </c>
       <c r="O13" t="n">
-        <v>56.2</v>
+        <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>15.881</v>
+        <v>7.264</v>
       </c>
       <c r="T13" t="n">
-        <v>13.069</v>
+        <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>74.419</v>
+        <v>86.517</v>
       </c>
       <c r="V13" t="n">
-        <v>98.842</v>
+        <v>86.517</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.838</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="14">
@@ -1553,7 +1601,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1566,55 +1614,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>-4.039576813106816</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>-15.51412294404569</v>
+        <v>-2.485427176837574</v>
       </c>
       <c r="K14" t="n">
-        <v>14.16764711666048</v>
+        <v>31.11411326152826</v>
       </c>
       <c r="L14" t="n">
-        <v>22.8370162826819</v>
+        <v>7.879921591535</v>
       </c>
       <c r="M14" t="n">
-        <v>77.77777777777779</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N14" t="n">
-        <v>45.1</v>
+        <v>14.5</v>
       </c>
       <c r="O14" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>15.882</v>
+        <v>7.264</v>
       </c>
       <c r="T14" t="n">
-        <v>12.892</v>
+        <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>56.024</v>
+        <v>86.517</v>
       </c>
       <c r="V14" t="n">
-        <v>77.873</v>
+        <v>86.517</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.222</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="16">
@@ -1744,17 +1804,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 | 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1770,29 +1830,29 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>49.35390788200862</v>
+        <v>50.31783953782316</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>14.53607138314319</v>
+        <v>10.77487934152495</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.915826539070666</v>
+        <v>5.194089911712285</v>
       </c>
       <c r="L18" t="n">
-        <v>16.46690178496608</v>
+        <v>19.33725726507755</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="O18" t="n">
-        <v>47.1</v>
+        <v>51.8</v>
       </c>
       <c r="P18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1803,35 +1863,35 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="T18" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>61.402</v>
+        <v>168.209</v>
       </c>
       <c r="V18" t="n">
-        <v>74.371</v>
+        <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-22.795</v>
+        <v>-23.133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1847,29 +1907,29 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>46.89202291173533</v>
+        <v>46.94985892607355</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>20.23942766288032</v>
+        <v>22.59150134949037</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3272617918051557</v>
+        <v>-1.195399439619516</v>
       </c>
       <c r="L19" t="n">
-        <v>8.076882947230402</v>
+        <v>14.54467229027953</v>
       </c>
       <c r="M19" t="n">
-        <v>72.22222222222221</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>42.2</v>
+        <v>148</v>
       </c>
       <c r="O19" t="n">
-        <v>62.4</v>
+        <v>53.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1880,35 +1940,35 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="T19" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>34.682</v>
+        <v>84.146</v>
       </c>
       <c r="V19" t="n">
-        <v>20.464</v>
+        <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.13</v>
+        <v>-13.132</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 | 2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S5|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1924,29 +1984,29 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>44.24447097072779</v>
+        <v>46.50482418007029</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>16.3270873608562</v>
+        <v>22.22039417483554</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.202916842117645</v>
+        <v>-1.195399439619493</v>
       </c>
       <c r="L20" t="n">
-        <v>8.338915824512183</v>
+        <v>13.82158293080772</v>
       </c>
       <c r="M20" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>49.1</v>
+        <v>147</v>
       </c>
       <c r="O20" t="n">
-        <v>57.6</v>
+        <v>53.4</v>
       </c>
       <c r="P20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1957,35 +2017,35 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="T20" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>30.889</v>
+        <v>81.583</v>
       </c>
       <c r="V20" t="n">
-        <v>21.157</v>
+        <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.656000000000001</v>
+        <v>-12.949</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2001,29 +2061,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>11.64377880826557</v>
+        <v>38.94248592369556</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>6.729894491660082</v>
+        <v>15.08563954368505</v>
       </c>
       <c r="K21" t="n">
-        <v>0.231855628775679</v>
+        <v>-7.289275987144639</v>
       </c>
       <c r="L21" t="n">
-        <v>5.137942413230245</v>
+        <v>12.5804569568174</v>
       </c>
       <c r="M21" t="n">
-        <v>38.88888888888889</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>17.9</v>
+        <v>76.5</v>
       </c>
       <c r="O21" t="n">
-        <v>58.3</v>
+        <v>48.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2034,35 +2094,35 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>8.561</v>
+        <v>12.325</v>
       </c>
       <c r="T21" t="n">
-        <v>8.561</v>
+        <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>46.219</v>
+        <v>78.52</v>
       </c>
       <c r="V21" t="n">
-        <v>39.702</v>
+        <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.629</v>
+        <v>-23.493</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2078,29 +2138,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.08861058164342239</v>
+        <v>31.10445507363087</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>-8.202644821914962</v>
+        <v>2.246452219851824</v>
       </c>
       <c r="K22" t="n">
-        <v>19.34320396880098</v>
+        <v>4.590130482453136</v>
       </c>
       <c r="L22" t="n">
-        <v>16.0458828125</v>
+        <v>17.92592565753429</v>
       </c>
       <c r="M22" t="n">
-        <v>66.66666666666666</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>26.8</v>
+        <v>60.5</v>
       </c>
       <c r="O22" t="n">
-        <v>53.7</v>
+        <v>54.5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2111,25 +2171,25 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>20.787</v>
+        <v>15.835</v>
       </c>
       <c r="T22" t="n">
-        <v>20.787</v>
+        <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>86.48399999999999</v>
+        <v>130.51</v>
       </c>
       <c r="V22" t="n">
-        <v>85.959</v>
+        <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.378</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2139,7 +2199,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2152,132 +2212,500 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MRVL, MU</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>-4.039576813106816</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>26.20489633670095</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>-15.51412294404569</v>
+        <v>9.984984890543625</v>
       </c>
       <c r="K23" t="n">
-        <v>14.16764711666048</v>
+        <v>6.752234869836449</v>
       </c>
       <c r="L23" t="n">
-        <v>22.8370162826819</v>
+        <v>18.40557500086005</v>
       </c>
       <c r="M23" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>45.1</v>
+        <v>164.5</v>
       </c>
       <c r="O23" t="n">
-        <v>56</v>
+        <v>51.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>15.882</v>
+        <v>23.406</v>
       </c>
       <c r="T23" t="n">
-        <v>12.892</v>
+        <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>56.024</v>
+        <v>24.858</v>
       </c>
       <c r="V23" t="n">
-        <v>77.873</v>
+        <v>19.426</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.222</v>
+        <v>-11.181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>DD_KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>APH, COP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>25.00234807668962</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>7.003544895075797</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.42099904130386</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3.457636701004341</v>
+      </c>
+      <c r="M24" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N24" t="n">
+        <v>22</v>
+      </c>
+      <c r="O24" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8.563000000000001</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8.563000000000001</v>
+      </c>
+      <c r="U24" t="n">
+        <v>49.157</v>
+      </c>
+      <c r="V24" t="n">
+        <v>49.157</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-11.175</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DD_KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|hacim_kirilim</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>20.20832547812279</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>8.328099283309044</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.3873406760593223</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.876696273694236</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="N25" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.651</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.619</v>
+      </c>
+      <c r="U25" t="n">
+        <v>36.485</v>
+      </c>
+      <c r="V25" t="n">
+        <v>30.326</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>LAST_3_TOP3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.485427176837574</v>
+      </c>
+      <c r="K26" t="n">
+        <v>31.11411326152826</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.879921591535</v>
+      </c>
+      <c r="M26" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>69</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="U26" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="V26" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.075</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>-5.737726850587677</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>-15.51355971349434</v>
-      </c>
-      <c r="K24" t="n">
-        <v>14.16765759127694</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22.83624131316222</v>
-      </c>
-      <c r="M24" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N24" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>15.881</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13.069</v>
-      </c>
-      <c r="U24" t="n">
-        <v>74.419</v>
-      </c>
-      <c r="V24" t="n">
-        <v>98.842</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-5.838</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.485427176837574</v>
+      </c>
+      <c r="K27" t="n">
+        <v>31.11411326152826</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.879921591535</v>
+      </c>
+      <c r="M27" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>69</v>
+      </c>
+      <c r="P27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="U27" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="V27" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.075</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.485427176837574</v>
+      </c>
+      <c r="K28" t="n">
+        <v>31.11411326152826</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.879921591535</v>
+      </c>
+      <c r="M28" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>69</v>
+      </c>
+      <c r="P28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="U28" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="V28" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.075</v>
       </c>
     </row>
   </sheetData>
@@ -2299,18 +2727,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -2462,7 +2890,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2478,29 +2906,29 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>49.35390788200862</v>
+        <v>50.31783953782316</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>14.53607138314319</v>
+        <v>10.77487934152495</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.915826539070666</v>
+        <v>5.194089911712285</v>
       </c>
       <c r="L3" t="n">
-        <v>16.46690178496608</v>
+        <v>19.33725726507755</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="O3" t="n">
-        <v>47.1</v>
+        <v>51.8</v>
       </c>
       <c r="P3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -2511,19 +2939,19 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="T3" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>61.402</v>
+        <v>168.209</v>
       </c>
       <c r="V3" t="n">
-        <v>74.371</v>
+        <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.795</v>
+        <v>-23.133</v>
       </c>
     </row>
     <row r="4">
@@ -2537,7 +2965,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2553,26 +2981,26 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>46.89202291173533</v>
+        <v>38.94248592369556</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>20.23942766288032</v>
+        <v>15.08563954368505</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3272617918051557</v>
+        <v>-7.289275987144639</v>
       </c>
       <c r="L4" t="n">
-        <v>8.076882947230402</v>
+        <v>12.5804569568174</v>
       </c>
       <c r="M4" t="n">
-        <v>72.22222222222221</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>42.2</v>
+        <v>76.5</v>
       </c>
       <c r="O4" t="n">
-        <v>62.4</v>
+        <v>48.4</v>
       </c>
       <c r="P4" t="n">
         <v>2.3</v>
@@ -2586,19 +3014,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>7.489</v>
+        <v>12.325</v>
       </c>
       <c r="T4" t="n">
-        <v>7.489</v>
+        <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>34.682</v>
+        <v>78.52</v>
       </c>
       <c r="V4" t="n">
-        <v>20.464</v>
+        <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.13</v>
+        <v>-23.493</v>
       </c>
     </row>
     <row r="5">
@@ -2612,7 +3040,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2628,29 +3056,29 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>44.24447097072779</v>
+        <v>31.10445507363087</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>16.3270873608562</v>
+        <v>2.246452219851824</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.202916842117645</v>
+        <v>4.590130482453136</v>
       </c>
       <c r="L5" t="n">
-        <v>8.338915824512183</v>
+        <v>17.92592565753429</v>
       </c>
       <c r="M5" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>49.1</v>
+        <v>60.5</v>
       </c>
       <c r="O5" t="n">
-        <v>57.6</v>
+        <v>54.5</v>
       </c>
       <c r="P5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -2661,19 +3089,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>9.178000000000001</v>
+        <v>15.835</v>
       </c>
       <c r="T5" t="n">
-        <v>9.178000000000001</v>
+        <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>30.889</v>
+        <v>130.51</v>
       </c>
       <c r="V5" t="n">
-        <v>21.157</v>
+        <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-8.656000000000001</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="6">
@@ -2687,7 +3115,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2703,29 +3131,29 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>46.89202291173533</v>
+        <v>46.94985892607355</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>20.23942766288032</v>
+        <v>22.59150134949037</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3272617918051557</v>
+        <v>-1.195399439619516</v>
       </c>
       <c r="L6" t="n">
-        <v>8.076882947230402</v>
+        <v>14.54467229027953</v>
       </c>
       <c r="M6" t="n">
-        <v>72.22222222222221</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>42.2</v>
+        <v>148</v>
       </c>
       <c r="O6" t="n">
-        <v>62.4</v>
+        <v>53.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -2736,19 +3164,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="T6" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>34.682</v>
+        <v>84.146</v>
       </c>
       <c r="V6" t="n">
-        <v>20.464</v>
+        <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.13</v>
+        <v>-13.132</v>
       </c>
     </row>
     <row r="7">
@@ -2762,7 +3190,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2778,29 +3206,29 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>44.24447097072779</v>
+        <v>38.94248592369556</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>16.3270873608562</v>
+        <v>15.08563954368505</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.202916842117645</v>
+        <v>-7.289275987144639</v>
       </c>
       <c r="L7" t="n">
-        <v>8.338915824512183</v>
+        <v>12.5804569568174</v>
       </c>
       <c r="M7" t="n">
-        <v>83.33333333333334</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>49.1</v>
+        <v>76.5</v>
       </c>
       <c r="O7" t="n">
-        <v>57.6</v>
+        <v>48.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -2811,19 +3239,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>9.178000000000001</v>
+        <v>12.325</v>
       </c>
       <c r="T7" t="n">
-        <v>9.178000000000001</v>
+        <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>30.889</v>
+        <v>78.52</v>
       </c>
       <c r="V7" t="n">
-        <v>21.157</v>
+        <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-8.656000000000001</v>
+        <v>-23.493</v>
       </c>
     </row>
     <row r="8">
@@ -2837,7 +3265,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2850,55 +3278,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MRVL, MU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>49.35390788200862</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>26.20489633670095</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>14.53607138314319</v>
+        <v>9.984984890543625</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.915826539070666</v>
+        <v>6.752234869836449</v>
       </c>
       <c r="L8" t="n">
-        <v>16.46690178496608</v>
+        <v>18.40557500086005</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>84.3</v>
+        <v>164.5</v>
       </c>
       <c r="O8" t="n">
-        <v>47.1</v>
+        <v>51.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>19.429</v>
+        <v>23.406</v>
       </c>
       <c r="T8" t="n">
-        <v>19.429</v>
+        <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>61.402</v>
+        <v>24.858</v>
       </c>
       <c r="V8" t="n">
-        <v>74.371</v>
+        <v>19.426</v>
       </c>
       <c r="W8" t="n">
-        <v>-22.795</v>
+        <v>-11.181</v>
       </c>
     </row>
     <row r="9">
@@ -2912,7 +3352,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|hacim_kirilim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2928,29 +3368,29 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>46.89202291173533</v>
+        <v>20.20832547812279</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>20.23942766288032</v>
+        <v>8.328099283309044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3272617918051557</v>
+        <v>-0.3873406760593223</v>
       </c>
       <c r="L9" t="n">
-        <v>8.076882947230402</v>
+        <v>4.876696273694236</v>
       </c>
       <c r="M9" t="n">
-        <v>72.22222222222221</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>42.2</v>
+        <v>41.5</v>
       </c>
       <c r="O9" t="n">
-        <v>62.4</v>
+        <v>45.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -2961,19 +3401,19 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>7.489</v>
+        <v>4.651</v>
       </c>
       <c r="T9" t="n">
-        <v>7.489</v>
+        <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>34.682</v>
+        <v>36.485</v>
       </c>
       <c r="V9" t="n">
-        <v>20.464</v>
+        <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.13</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="10">
@@ -2987,7 +3427,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S5|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3003,29 +3443,29 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>44.24447097072779</v>
+        <v>46.50482418007029</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>16.3270873608562</v>
+        <v>22.22039417483554</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.202916842117645</v>
+        <v>-1.195399439619493</v>
       </c>
       <c r="L10" t="n">
-        <v>8.338915824512183</v>
+        <v>13.82158293080772</v>
       </c>
       <c r="M10" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>49.1</v>
+        <v>147</v>
       </c>
       <c r="O10" t="n">
-        <v>57.6</v>
+        <v>53.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -3036,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="T10" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>30.889</v>
+        <v>81.583</v>
       </c>
       <c r="V10" t="n">
-        <v>21.157</v>
+        <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-8.656000000000001</v>
+        <v>-12.949</v>
       </c>
     </row>
     <row r="11">
@@ -3062,7 +3502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3075,55 +3515,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>APH, COP</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>11.64377880826557</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>25.00234807668962</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
       <c r="J11" t="n">
-        <v>6.729894491660082</v>
+        <v>7.003544895075797</v>
       </c>
       <c r="K11" t="n">
-        <v>0.231855628775679</v>
+        <v>0.42099904130386</v>
       </c>
       <c r="L11" t="n">
-        <v>5.137942413230245</v>
+        <v>3.457636701004341</v>
       </c>
       <c r="M11" t="n">
-        <v>38.88888888888889</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>17.9</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>58.3</v>
+        <v>63.6</v>
       </c>
       <c r="P11" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>8.561</v>
+        <v>8.563000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>8.561</v>
+        <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>46.219</v>
+        <v>49.157</v>
       </c>
       <c r="V11" t="n">
-        <v>39.702</v>
+        <v>49.157</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.629</v>
+        <v>-11.175</v>
       </c>
     </row>
     <row r="12">
@@ -3137,7 +3589,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3150,55 +3602,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>0.08861058164342239</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>-8.202644821914962</v>
+        <v>-2.485427176837574</v>
       </c>
       <c r="K12" t="n">
-        <v>19.34320396880098</v>
+        <v>31.11411326152826</v>
       </c>
       <c r="L12" t="n">
-        <v>16.0458828125</v>
+        <v>7.879921591535</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666666</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N12" t="n">
-        <v>26.8</v>
+        <v>14.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53.7</v>
+        <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>20.787</v>
+        <v>7.264</v>
       </c>
       <c r="T12" t="n">
-        <v>20.787</v>
+        <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>86.48399999999999</v>
+        <v>86.517</v>
       </c>
       <c r="V12" t="n">
-        <v>85.959</v>
+        <v>86.517</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.378</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="13">
@@ -3212,7 +3676,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3225,55 +3689,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>-5.737726850587677</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>-15.51355971349434</v>
+        <v>-2.485427176837574</v>
       </c>
       <c r="K13" t="n">
-        <v>14.16765759127694</v>
+        <v>31.11411326152826</v>
       </c>
       <c r="L13" t="n">
-        <v>22.83624131316222</v>
+        <v>7.879921591535</v>
       </c>
       <c r="M13" t="n">
-        <v>77.77777777777779</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N13" t="n">
-        <v>47.6</v>
+        <v>14.5</v>
       </c>
       <c r="O13" t="n">
-        <v>56.2</v>
+        <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>15.881</v>
+        <v>7.264</v>
       </c>
       <c r="T13" t="n">
-        <v>13.069</v>
+        <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>74.419</v>
+        <v>86.517</v>
       </c>
       <c r="V13" t="n">
-        <v>98.842</v>
+        <v>86.517</v>
       </c>
       <c r="W13" t="n">
-        <v>-5.838</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="14">
@@ -3287,7 +3763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3300,55 +3776,67 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>-4.039576813106816</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>-15.51412294404569</v>
+        <v>-2.485427176837574</v>
       </c>
       <c r="K14" t="n">
-        <v>14.16764711666048</v>
+        <v>31.11411326152826</v>
       </c>
       <c r="L14" t="n">
-        <v>22.8370162826819</v>
+        <v>7.879921591535</v>
       </c>
       <c r="M14" t="n">
-        <v>77.77777777777779</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="N14" t="n">
-        <v>45.1</v>
+        <v>14.5</v>
       </c>
       <c r="O14" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>15.882</v>
+        <v>7.264</v>
       </c>
       <c r="T14" t="n">
-        <v>12.892</v>
+        <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>56.024</v>
+        <v>86.517</v>
       </c>
       <c r="V14" t="n">
-        <v>77.873</v>
+        <v>86.517</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.222</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="16">
@@ -3478,17 +3966,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 | 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2_rotasyon|E30|S2|M30|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan</t>
+          <t>T5_tek_sistem|E50|S3|M30|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3504,29 +3992,29 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>49.35390788200862</v>
+        <v>50.31783953782316</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>14.53607138314319</v>
+        <v>10.77487934152495</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.915826539070666</v>
+        <v>5.194089911712285</v>
       </c>
       <c r="L18" t="n">
-        <v>16.46690178496608</v>
+        <v>19.33725726507755</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="O18" t="n">
-        <v>47.1</v>
+        <v>51.8</v>
       </c>
       <c r="P18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3537,35 +4025,35 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="T18" t="n">
-        <v>19.429</v>
+        <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>61.402</v>
+        <v>168.209</v>
       </c>
       <c r="V18" t="n">
-        <v>74.371</v>
+        <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-22.795</v>
+        <v>-23.133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2 | 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|geri_cekilme</t>
+          <t>T5_tek_sistem|E50|S5|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3581,29 +4069,29 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>46.89202291173533</v>
+        <v>46.94985892607355</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>20.23942766288032</v>
+        <v>22.59150134949037</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3272617918051557</v>
+        <v>-1.195399439619516</v>
       </c>
       <c r="L19" t="n">
-        <v>8.076882947230402</v>
+        <v>14.54467229027953</v>
       </c>
       <c r="M19" t="n">
-        <v>72.22222222222221</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>42.2</v>
+        <v>148</v>
       </c>
       <c r="O19" t="n">
-        <v>62.4</v>
+        <v>53.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3614,35 +4102,35 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="T19" t="n">
-        <v>7.489</v>
+        <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>34.682</v>
+        <v>84.146</v>
       </c>
       <c r="V19" t="n">
-        <v>20.464</v>
+        <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.13</v>
+        <v>-13.132</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3 | DD_KAR_TOP3</t>
+          <t>DD_KAR_TOP3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 | 2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S5|M30|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|keltner_kirilim</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3658,29 +4146,29 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>44.24447097072779</v>
+        <v>46.50482418007029</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>16.3270873608562</v>
+        <v>22.22039417483554</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.202916842117645</v>
+        <v>-1.195399439619493</v>
       </c>
       <c r="L20" t="n">
-        <v>8.338915824512183</v>
+        <v>13.82158293080772</v>
       </c>
       <c r="M20" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>49.1</v>
+        <v>147</v>
       </c>
       <c r="O20" t="n">
-        <v>57.6</v>
+        <v>53.4</v>
       </c>
       <c r="P20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3691,35 +4179,35 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="T20" t="n">
-        <v>9.178000000000001</v>
+        <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>30.889</v>
+        <v>81.583</v>
       </c>
       <c r="V20" t="n">
-        <v>21.157</v>
+        <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.656000000000001</v>
+        <v>-12.949</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DD_KAR_TOP3</t>
+          <t>KAR_TOP3 | IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T4_konsensus|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Pskor</t>
+          <t>T5_tek_sistem|E50|S2|M50|esit|TR0.0|TP0.05|KT0.03|KC0.05|Gsistem_ort|Pskor|hacim_kirilim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3735,29 +4223,29 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>11.64377880826557</v>
+        <v>38.94248592369556</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>6.729894491660082</v>
+        <v>15.08563954368505</v>
       </c>
       <c r="K21" t="n">
-        <v>0.231855628775679</v>
+        <v>-7.289275987144639</v>
       </c>
       <c r="L21" t="n">
-        <v>5.137942413230245</v>
+        <v>12.5804569568174</v>
       </c>
       <c r="M21" t="n">
-        <v>38.88888888888889</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>17.9</v>
+        <v>76.5</v>
       </c>
       <c r="O21" t="n">
-        <v>58.3</v>
+        <v>48.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3768,35 +4256,35 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>8.561</v>
+        <v>12.325</v>
       </c>
       <c r="T21" t="n">
-        <v>8.561</v>
+        <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>46.219</v>
+        <v>78.52</v>
       </c>
       <c r="V21" t="n">
-        <v>39.702</v>
+        <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.629</v>
+        <v>-23.493</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>KAR_TOP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T5_tek_sistem|E50|S2|M20|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|keltner_kirilim</t>
+          <t>T5_tek_sistem|E50|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Pskor|coklu_zarf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3812,29 +4300,29 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.08861058164342239</v>
+        <v>31.10445507363087</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>-8.202644821914962</v>
+        <v>2.246452219851824</v>
       </c>
       <c r="K22" t="n">
-        <v>19.34320396880098</v>
+        <v>4.590130482453136</v>
       </c>
       <c r="L22" t="n">
-        <v>16.0458828125</v>
+        <v>17.92592565753429</v>
       </c>
       <c r="M22" t="n">
-        <v>66.66666666666666</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>26.8</v>
+        <v>60.5</v>
       </c>
       <c r="O22" t="n">
-        <v>53.7</v>
+        <v>54.5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3845,25 +4333,25 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>20.787</v>
+        <v>15.835</v>
       </c>
       <c r="T22" t="n">
-        <v>20.787</v>
+        <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>86.48399999999999</v>
+        <v>130.51</v>
       </c>
       <c r="V22" t="n">
-        <v>85.959</v>
+        <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.378</v>
+        <v>-0.221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAST_3_TOP3</t>
+          <t>IKI_AY_HARIC_CAGR_TOP3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3873,7 +4361,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T1_genislik_skor|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
+          <t>T6_skor_momentum|E30|S2|M50|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3886,132 +4374,500 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MRVL, MU</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>-4.039576813106816</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>26.20489633670095</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>-15.51412294404569</v>
+        <v>9.984984890543625</v>
       </c>
       <c r="K23" t="n">
-        <v>14.16764711666048</v>
+        <v>6.752234869836449</v>
       </c>
       <c r="L23" t="n">
-        <v>22.8370162826819</v>
+        <v>18.40557500086005</v>
       </c>
       <c r="M23" t="n">
-        <v>77.77777777777779</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>45.1</v>
+        <v>164.5</v>
       </c>
       <c r="O23" t="n">
-        <v>56</v>
+        <v>51.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NAKIT_SINYAL_YOK</t>
+          <t>ACIK</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>15.882</v>
+        <v>23.406</v>
       </c>
       <c r="T23" t="n">
-        <v>12.892</v>
+        <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>56.024</v>
+        <v>24.858</v>
       </c>
       <c r="V23" t="n">
-        <v>77.873</v>
+        <v>19.426</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.222</v>
+        <v>-11.181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>DD_KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M20|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Pskor|coklu_zarf</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>APH, COP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>25.00234807668962</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>7.003544895075797</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.42099904130386</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3.457636701004341</v>
+      </c>
+      <c r="M24" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N24" t="n">
+        <v>22</v>
+      </c>
+      <c r="O24" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8.563000000000001</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8.563000000000001</v>
+      </c>
+      <c r="U24" t="n">
+        <v>49.157</v>
+      </c>
+      <c r="V24" t="n">
+        <v>49.157</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-11.175</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DD_KAR_TOP3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E50|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.05|Gsistem_ort|Ppuan|Bvolatilite|hacim_kirilim</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>20.20832547812279</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>8.328099283309044</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.3873406760593223</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.876696273694236</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="N25" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>NAKIT_SINYAL_YOK</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.651</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.619</v>
+      </c>
+      <c r="U25" t="n">
+        <v>36.485</v>
+      </c>
+      <c r="V25" t="n">
+        <v>30.326</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>LAST_3_TOP3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>T1_genislik_skor|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.485427176837574</v>
+      </c>
+      <c r="K26" t="n">
+        <v>31.11411326152826</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.879921591535</v>
+      </c>
+      <c r="M26" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>69</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="U26" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="V26" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.075</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>T2_rotasyon|E50|S2|M50|performans|TR0.0|TP0.0|KT0.03|KC0.0|Gsistem_ort|Ppuan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T3_kademeli_slot|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>-5.737726850587677</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>-15.51355971349434</v>
-      </c>
-      <c r="K24" t="n">
-        <v>14.16765759127694</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22.83624131316222</v>
-      </c>
-      <c r="M24" t="n">
-        <v>77.77777777777779</v>
-      </c>
-      <c r="N24" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>NAKIT_SINYAL_YOK</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>15.881</v>
-      </c>
-      <c r="T24" t="n">
-        <v>13.069</v>
-      </c>
-      <c r="U24" t="n">
-        <v>74.419</v>
-      </c>
-      <c r="V24" t="n">
-        <v>98.842</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-5.838</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.485427176837574</v>
+      </c>
+      <c r="K27" t="n">
+        <v>31.11411326152826</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.879921591535</v>
+      </c>
+      <c r="M27" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>69</v>
+      </c>
+      <c r="P27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="U27" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="V27" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.075</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LAST_3_TOP3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>T5_tek_sistem|E30|S2|M0|esit|TR0.0|TP0.0|KT0.03|KC0.0|Gskor|Ppuan|vidya_trend</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PLTR, SMCI</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PLTR: 2026-08-06 | SMCI: 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>5.246879321893227</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.485427176837574</v>
+      </c>
+      <c r="K28" t="n">
+        <v>31.11411326152826</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.879921591535</v>
+      </c>
+      <c r="M28" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="N28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>69</v>
+      </c>
+      <c r="P28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7.264</v>
+      </c>
+      <c r="U28" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="V28" t="n">
+        <v>86.517</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.075</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -744,17 +744,17 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>50.31783953782316</v>
+        <v>50.31784332199509</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>10.77487934152495</v>
+        <v>10.77488073998969</v>
       </c>
       <c r="K3" t="n">
-        <v>5.194089911712285</v>
+        <v>5.194092094852287</v>
       </c>
       <c r="L3" t="n">
-        <v>19.33725726507755</v>
+        <v>19.3372566026348</v>
       </c>
       <c r="M3" t="n">
         <v>94.44444444444444</v>
@@ -819,17 +819,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>38.94248592369556</v>
+        <v>38.94248609117772</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>15.08563954368505</v>
+        <v>15.08563547208812</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.289275987144639</v>
+        <v>-7.289272668386781</v>
       </c>
       <c r="L4" t="n">
-        <v>12.5804569568174</v>
+        <v>12.58045446527185</v>
       </c>
       <c r="M4" t="n">
         <v>88.88888888888889</v>
@@ -894,17 +894,17 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>31.10445507363087</v>
+        <v>31.10445432646189</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>2.246452219851824</v>
+        <v>2.246453681178617</v>
       </c>
       <c r="K5" t="n">
-        <v>4.590130482453136</v>
+        <v>4.590127419986811</v>
       </c>
       <c r="L5" t="n">
-        <v>17.92592565753429</v>
+        <v>17.92592436767892</v>
       </c>
       <c r="M5" t="n">
         <v>94.44444444444444</v>
@@ -969,17 +969,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>46.94985892607355</v>
+        <v>46.94985784166392</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>22.59150134949037</v>
+        <v>22.59150141392472</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.195399439619516</v>
+        <v>-1.195397465411052</v>
       </c>
       <c r="L6" t="n">
-        <v>14.54467229027953</v>
+        <v>14.5446668661262</v>
       </c>
       <c r="M6" t="n">
         <v>94.44444444444444</v>
@@ -1044,17 +1044,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>38.94248592369556</v>
+        <v>38.94248609117772</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>15.08563954368505</v>
+        <v>15.08563547208812</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.289275987144639</v>
+        <v>-7.289272668386781</v>
       </c>
       <c r="L7" t="n">
-        <v>12.5804569568174</v>
+        <v>12.58045446527185</v>
       </c>
       <c r="M7" t="n">
         <v>88.88888888888889</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26.20489633670095</v>
+        <v>26.20489804290218</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9.984984890543625</v>
+        <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>6.752234869836449</v>
+        <v>6.752239299334195</v>
       </c>
       <c r="L8" t="n">
-        <v>18.40557500086005</v>
+        <v>18.40557264012871</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -1206,17 +1206,17 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>20.20832547812279</v>
+        <v>20.20832698267658</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>8.328099283309044</v>
+        <v>8.32809964878245</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3873406760593223</v>
+        <v>-0.387340012031856</v>
       </c>
       <c r="L9" t="n">
-        <v>4.876696273694236</v>
+        <v>4.87669639435675</v>
       </c>
       <c r="M9" t="n">
         <v>88.88888888888889</v>
@@ -1281,17 +1281,17 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>46.50482418007029</v>
+        <v>46.50482746377295</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>22.22039417483554</v>
+        <v>22.2204024316784</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.195399439619493</v>
+        <v>-1.195401606073943</v>
       </c>
       <c r="L10" t="n">
-        <v>13.82158293080772</v>
+        <v>13.82158181157557</v>
       </c>
       <c r="M10" t="n">
         <v>94.44444444444444</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>25.00234807668962</v>
+        <v>25.00234869887699</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7.003544895075797</v>
+        <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.42099904130386</v>
+        <v>0.4209968749445014</v>
       </c>
       <c r="L11" t="n">
-        <v>3.457636701004341</v>
+        <v>3.457635521851321</v>
       </c>
       <c r="M11" t="n">
         <v>27.77777777777778</v>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L12" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M12" t="n">
         <v>27.77777777777778</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L13" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M13" t="n">
         <v>27.77777777777778</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L14" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M14" t="n">
         <v>27.77777777777778</v>
@@ -1830,17 +1830,17 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>50.31783953782316</v>
+        <v>50.31784332199509</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>10.77487934152495</v>
+        <v>10.77488073998969</v>
       </c>
       <c r="K18" t="n">
-        <v>5.194089911712285</v>
+        <v>5.194092094852287</v>
       </c>
       <c r="L18" t="n">
-        <v>19.33725726507755</v>
+        <v>19.3372566026348</v>
       </c>
       <c r="M18" t="n">
         <v>94.44444444444444</v>
@@ -1907,17 +1907,17 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>46.94985892607355</v>
+        <v>46.94985784166392</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>22.59150134949037</v>
+        <v>22.59150141392472</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.195399439619516</v>
+        <v>-1.195397465411052</v>
       </c>
       <c r="L19" t="n">
-        <v>14.54467229027953</v>
+        <v>14.5446668661262</v>
       </c>
       <c r="M19" t="n">
         <v>94.44444444444444</v>
@@ -1984,17 +1984,17 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>46.50482418007029</v>
+        <v>46.50482746377295</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>22.22039417483554</v>
+        <v>22.2204024316784</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.195399439619493</v>
+        <v>-1.195401606073943</v>
       </c>
       <c r="L20" t="n">
-        <v>13.82158293080772</v>
+        <v>13.82158181157557</v>
       </c>
       <c r="M20" t="n">
         <v>94.44444444444444</v>
@@ -2061,17 +2061,17 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>38.94248592369556</v>
+        <v>38.94248609117772</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>15.08563954368505</v>
+        <v>15.08563547208812</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.289275987144639</v>
+        <v>-7.289272668386781</v>
       </c>
       <c r="L21" t="n">
-        <v>12.5804569568174</v>
+        <v>12.58045446527185</v>
       </c>
       <c r="M21" t="n">
         <v>88.88888888888889</v>
@@ -2138,17 +2138,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>31.10445507363087</v>
+        <v>31.10445432646189</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>2.246452219851824</v>
+        <v>2.246453681178617</v>
       </c>
       <c r="K22" t="n">
-        <v>4.590130482453136</v>
+        <v>4.590127419986811</v>
       </c>
       <c r="L22" t="n">
-        <v>17.92592565753429</v>
+        <v>17.92592436767892</v>
       </c>
       <c r="M22" t="n">
         <v>94.44444444444444</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>26.20489633670095</v>
+        <v>26.20489804290218</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>9.984984890543625</v>
+        <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>6.752234869836449</v>
+        <v>6.752239299334195</v>
       </c>
       <c r="L23" t="n">
-        <v>18.40557500086005</v>
+        <v>18.40557264012871</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25.00234807668962</v>
+        <v>25.00234869887699</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7.003544895075797</v>
+        <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.42099904130386</v>
+        <v>0.4209968749445014</v>
       </c>
       <c r="L24" t="n">
-        <v>3.457636701004341</v>
+        <v>3.457635521851321</v>
       </c>
       <c r="M24" t="n">
         <v>27.77777777777778</v>
@@ -2393,17 +2393,17 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>20.20832547812279</v>
+        <v>20.20832698267658</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>8.328099283309044</v>
+        <v>8.32809964878245</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3873406760593223</v>
+        <v>-0.387340012031856</v>
       </c>
       <c r="L25" t="n">
-        <v>4.876696273694236</v>
+        <v>4.87669639435675</v>
       </c>
       <c r="M25" t="n">
         <v>88.88888888888889</v>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2486,13 +2486,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L26" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M26" t="n">
         <v>27.77777777777778</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L27" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M27" t="n">
         <v>27.77777777777778</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L28" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M28" t="n">
         <v>27.77777777777778</v>
@@ -2906,17 +2906,17 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>50.31783953782316</v>
+        <v>50.31784332199509</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>10.77487934152495</v>
+        <v>10.77488073998969</v>
       </c>
       <c r="K3" t="n">
-        <v>5.194089911712285</v>
+        <v>5.194092094852287</v>
       </c>
       <c r="L3" t="n">
-        <v>19.33725726507755</v>
+        <v>19.3372566026348</v>
       </c>
       <c r="M3" t="n">
         <v>94.44444444444444</v>
@@ -2981,17 +2981,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>38.94248592369556</v>
+        <v>38.94248609117772</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>15.08563954368505</v>
+        <v>15.08563547208812</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.289275987144639</v>
+        <v>-7.289272668386781</v>
       </c>
       <c r="L4" t="n">
-        <v>12.5804569568174</v>
+        <v>12.58045446527185</v>
       </c>
       <c r="M4" t="n">
         <v>88.88888888888889</v>
@@ -3056,17 +3056,17 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>31.10445507363087</v>
+        <v>31.10445432646189</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>2.246452219851824</v>
+        <v>2.246453681178617</v>
       </c>
       <c r="K5" t="n">
-        <v>4.590130482453136</v>
+        <v>4.590127419986811</v>
       </c>
       <c r="L5" t="n">
-        <v>17.92592565753429</v>
+        <v>17.92592436767892</v>
       </c>
       <c r="M5" t="n">
         <v>94.44444444444444</v>
@@ -3131,17 +3131,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>46.94985892607355</v>
+        <v>46.94985784166392</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>22.59150134949037</v>
+        <v>22.59150141392472</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.195399439619516</v>
+        <v>-1.195397465411052</v>
       </c>
       <c r="L6" t="n">
-        <v>14.54467229027953</v>
+        <v>14.5446668661262</v>
       </c>
       <c r="M6" t="n">
         <v>94.44444444444444</v>
@@ -3206,17 +3206,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>38.94248592369556</v>
+        <v>38.94248609117772</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>15.08563954368505</v>
+        <v>15.08563547208812</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.289275987144639</v>
+        <v>-7.289272668386781</v>
       </c>
       <c r="L7" t="n">
-        <v>12.5804569568174</v>
+        <v>12.58045446527185</v>
       </c>
       <c r="M7" t="n">
         <v>88.88888888888889</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26.20489633670095</v>
+        <v>26.20489804290218</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3297,13 +3297,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9.984984890543625</v>
+        <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>6.752234869836449</v>
+        <v>6.752239299334195</v>
       </c>
       <c r="L8" t="n">
-        <v>18.40557500086005</v>
+        <v>18.40557264012871</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -3368,17 +3368,17 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>20.20832547812279</v>
+        <v>20.20832698267658</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>8.328099283309044</v>
+        <v>8.32809964878245</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3873406760593223</v>
+        <v>-0.387340012031856</v>
       </c>
       <c r="L9" t="n">
-        <v>4.876696273694236</v>
+        <v>4.87669639435675</v>
       </c>
       <c r="M9" t="n">
         <v>88.88888888888889</v>
@@ -3443,17 +3443,17 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>46.50482418007029</v>
+        <v>46.50482746377295</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>22.22039417483554</v>
+        <v>22.2204024316784</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.195399439619493</v>
+        <v>-1.195401606073943</v>
       </c>
       <c r="L10" t="n">
-        <v>13.82158293080772</v>
+        <v>13.82158181157557</v>
       </c>
       <c r="M10" t="n">
         <v>94.44444444444444</v>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>25.00234807668962</v>
+        <v>25.00234869887699</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7.003544895075797</v>
+        <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.42099904130386</v>
+        <v>0.4209968749445014</v>
       </c>
       <c r="L11" t="n">
-        <v>3.457636701004341</v>
+        <v>3.457635521851321</v>
       </c>
       <c r="M11" t="n">
         <v>27.77777777777778</v>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L12" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M12" t="n">
         <v>27.77777777777778</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3708,13 +3708,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L13" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M13" t="n">
         <v>27.77777777777778</v>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L14" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M14" t="n">
         <v>27.77777777777778</v>
@@ -3992,17 +3992,17 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>50.31783953782316</v>
+        <v>50.31784332199509</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>10.77487934152495</v>
+        <v>10.77488073998969</v>
       </c>
       <c r="K18" t="n">
-        <v>5.194089911712285</v>
+        <v>5.194092094852287</v>
       </c>
       <c r="L18" t="n">
-        <v>19.33725726507755</v>
+        <v>19.3372566026348</v>
       </c>
       <c r="M18" t="n">
         <v>94.44444444444444</v>
@@ -4069,17 +4069,17 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>46.94985892607355</v>
+        <v>46.94985784166392</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>22.59150134949037</v>
+        <v>22.59150141392472</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.195399439619516</v>
+        <v>-1.195397465411052</v>
       </c>
       <c r="L19" t="n">
-        <v>14.54467229027953</v>
+        <v>14.5446668661262</v>
       </c>
       <c r="M19" t="n">
         <v>94.44444444444444</v>
@@ -4146,17 +4146,17 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>46.50482418007029</v>
+        <v>46.50482746377295</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>22.22039417483554</v>
+        <v>22.2204024316784</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.195399439619493</v>
+        <v>-1.195401606073943</v>
       </c>
       <c r="L20" t="n">
-        <v>13.82158293080772</v>
+        <v>13.82158181157557</v>
       </c>
       <c r="M20" t="n">
         <v>94.44444444444444</v>
@@ -4223,17 +4223,17 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>38.94248592369556</v>
+        <v>38.94248609117772</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>15.08563954368505</v>
+        <v>15.08563547208812</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.289275987144639</v>
+        <v>-7.289272668386781</v>
       </c>
       <c r="L21" t="n">
-        <v>12.5804569568174</v>
+        <v>12.58045446527185</v>
       </c>
       <c r="M21" t="n">
         <v>88.88888888888889</v>
@@ -4300,17 +4300,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>31.10445507363087</v>
+        <v>31.10445432646189</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>2.246452219851824</v>
+        <v>2.246453681178617</v>
       </c>
       <c r="K22" t="n">
-        <v>4.590130482453136</v>
+        <v>4.590127419986811</v>
       </c>
       <c r="L22" t="n">
-        <v>17.92592565753429</v>
+        <v>17.92592436767892</v>
       </c>
       <c r="M22" t="n">
         <v>94.44444444444444</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>26.20489633670095</v>
+        <v>26.20489804290218</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>9.984984890543625</v>
+        <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>6.752234869836449</v>
+        <v>6.752239299334195</v>
       </c>
       <c r="L23" t="n">
-        <v>18.40557500086005</v>
+        <v>18.40557264012871</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25.00234807668962</v>
+        <v>25.00234869887699</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4482,13 +4482,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7.003544895075797</v>
+        <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.42099904130386</v>
+        <v>0.4209968749445014</v>
       </c>
       <c r="L24" t="n">
-        <v>3.457636701004341</v>
+        <v>3.457635521851321</v>
       </c>
       <c r="M24" t="n">
         <v>27.77777777777778</v>
@@ -4555,17 +4555,17 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>20.20832547812279</v>
+        <v>20.20832698267658</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>8.328099283309044</v>
+        <v>8.32809964878245</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3873406760593223</v>
+        <v>-0.387340012031856</v>
       </c>
       <c r="L25" t="n">
-        <v>4.876696273694236</v>
+        <v>4.87669639435675</v>
       </c>
       <c r="M25" t="n">
         <v>88.88888888888889</v>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L26" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M26" t="n">
         <v>27.77777777777778</v>
@@ -4729,7 +4729,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4737,13 +4737,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L27" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M27" t="n">
         <v>27.77777777777778</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.246879321893227</v>
+        <v>5.246880510643059</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4826,13 +4826,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-2.485427176837574</v>
+        <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>31.11411326152826</v>
+        <v>31.11411253223759</v>
       </c>
       <c r="L28" t="n">
-        <v>7.879921591535</v>
+        <v>7.879924557280349</v>
       </c>
       <c r="M28" t="n">
         <v>27.77777777777778</v>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -578,7 +578,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -783,13 +783,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>168.209</v>
+        <v>169.096</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.133</v>
+        <v>-23.209</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -858,13 +858,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>78.52</v>
+        <v>79.871</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-23.493</v>
+        <v>-23.671</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -933,13 +933,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>130.51</v>
+        <v>128.779</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>148</v>
+        <v>147.4</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -1008,13 +1008,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>84.146</v>
+        <v>85.517</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.132</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -1083,13 +1083,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>78.52</v>
+        <v>79.871</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-23.493</v>
+        <v>-23.671</v>
       </c>
     </row>
     <row r="8">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MRVL, MU</t>
+          <t>ADI, NOW</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1131,14 +1131,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>6.752239299334195</v>
+        <v>10.31363400333991</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -1147,10 +1147,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.5</v>
+        <v>164.8</v>
       </c>
       <c r="O8" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -1170,13 +1170,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>24.858</v>
+        <v>26.484</v>
       </c>
       <c r="V8" t="n">
-        <v>19.426</v>
+        <v>23.41</v>
       </c>
       <c r="W8" t="n">
-        <v>-11.181</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="9">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="O9" t="n">
         <v>45.8</v>
@@ -1245,13 +1245,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>36.485</v>
+        <v>36.688</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.36</v>
+        <v>-3.365</v>
       </c>
     </row>
     <row r="10">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>147</v>
+        <v>146.4</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -1320,13 +1320,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>81.583</v>
+        <v>83.239</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.949</v>
+        <v>-13.067</v>
       </c>
     </row>
     <row r="11">
@@ -1345,22 +1345,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>APH, COP</t>
+          <t>AMZN, APH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1368,14 +1368,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4209968749445014</v>
+        <v>-0.1230632240592611</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -1384,10 +1384,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="O11" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -1407,13 +1407,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="V11" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.175</v>
+        <v>-11.983</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -1471,13 +1471,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N12" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O12" t="n">
         <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V12" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -1558,13 +1558,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N13" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O13" t="n">
         <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1581,13 +1581,13 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V13" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -1645,13 +1645,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N14" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O14" t="n">
         <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1668,13 +1668,13 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V14" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -1869,13 +1869,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>168.209</v>
+        <v>169.096</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.133</v>
+        <v>-23.209</v>
       </c>
     </row>
     <row r="19">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>148</v>
+        <v>147.4</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -1946,13 +1946,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>84.146</v>
+        <v>85.517</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-13.132</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="20">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>147</v>
+        <v>146.4</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -2023,13 +2023,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>81.583</v>
+        <v>83.239</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.949</v>
+        <v>-13.067</v>
       </c>
     </row>
     <row r="21">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -2100,13 +2100,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>78.52</v>
+        <v>79.871</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.493</v>
+        <v>-23.671</v>
       </c>
     </row>
     <row r="22">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -2177,13 +2177,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>130.51</v>
+        <v>128.779</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="23">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MRVL, MU</t>
+          <t>ADI, NOW</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>6.752239299334195</v>
+        <v>10.31363400333991</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -2243,10 +2243,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.5</v>
+        <v>164.8</v>
       </c>
       <c r="O23" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -2266,13 +2266,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>24.858</v>
+        <v>26.484</v>
       </c>
       <c r="V23" t="n">
-        <v>19.426</v>
+        <v>23.41</v>
       </c>
       <c r="W23" t="n">
-        <v>-11.181</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="24">
@@ -2293,22 +2293,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>APH, COP</t>
+          <t>AMZN, APH</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4209968749445014</v>
+        <v>-0.1230632240592611</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -2332,10 +2332,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N24" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="O24" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -2355,13 +2355,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="V24" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.175</v>
+        <v>-11.983</v>
       </c>
     </row>
     <row r="25">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="O25" t="n">
         <v>45.8</v>
@@ -2432,13 +2432,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>36.485</v>
+        <v>36.688</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.36</v>
+        <v>-3.365</v>
       </c>
     </row>
     <row r="26">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -2498,13 +2498,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N26" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O26" t="n">
         <v>69</v>
       </c>
       <c r="P26" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2521,13 +2521,13 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V26" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -2587,13 +2587,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N27" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O27" t="n">
         <v>69</v>
       </c>
       <c r="P27" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2610,13 +2610,13 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V27" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -2676,13 +2676,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N28" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O28" t="n">
         <v>69</v>
       </c>
       <c r="P28" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2699,13 +2699,13 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V28" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2740,7 +2740,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -2945,13 +2945,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>168.209</v>
+        <v>169.096</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.133</v>
+        <v>-23.209</v>
       </c>
     </row>
     <row r="4">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -3020,13 +3020,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>78.52</v>
+        <v>79.871</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-23.493</v>
+        <v>-23.671</v>
       </c>
     </row>
     <row r="5">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -3095,13 +3095,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>130.51</v>
+        <v>128.779</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="6">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>148</v>
+        <v>147.4</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -3170,13 +3170,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>84.146</v>
+        <v>85.517</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.132</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="7">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -3245,13 +3245,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>78.52</v>
+        <v>79.871</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-23.493</v>
+        <v>-23.671</v>
       </c>
     </row>
     <row r="8">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MRVL, MU</t>
+          <t>ADI, NOW</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>6.752239299334195</v>
+        <v>10.31363400333991</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -3309,10 +3309,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.5</v>
+        <v>164.8</v>
       </c>
       <c r="O8" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -3332,13 +3332,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>24.858</v>
+        <v>26.484</v>
       </c>
       <c r="V8" t="n">
-        <v>19.426</v>
+        <v>23.41</v>
       </c>
       <c r="W8" t="n">
-        <v>-11.181</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="9">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="O9" t="n">
         <v>45.8</v>
@@ -3407,13 +3407,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>36.485</v>
+        <v>36.688</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.36</v>
+        <v>-3.365</v>
       </c>
     </row>
     <row r="10">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>147</v>
+        <v>146.4</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -3482,13 +3482,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>81.583</v>
+        <v>83.239</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.949</v>
+        <v>-13.067</v>
       </c>
     </row>
     <row r="11">
@@ -3507,22 +3507,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>APH, COP</t>
+          <t>AMZN, APH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4209968749445014</v>
+        <v>-0.1230632240592611</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -3546,10 +3546,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="O11" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -3569,13 +3569,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="V11" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.175</v>
+        <v>-11.983</v>
       </c>
     </row>
     <row r="12">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -3633,13 +3633,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N12" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O12" t="n">
         <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3656,13 +3656,13 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V12" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -3720,13 +3720,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N13" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O13" t="n">
         <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3743,13 +3743,13 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V13" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -3807,13 +3807,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N14" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O14" t="n">
         <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3830,13 +3830,13 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V14" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4008,7 +4008,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -4031,13 +4031,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>168.209</v>
+        <v>169.096</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.133</v>
+        <v>-23.209</v>
       </c>
     </row>
     <row r="19">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>148</v>
+        <v>147.4</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -4108,13 +4108,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>84.146</v>
+        <v>85.517</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-13.132</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="20">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>147</v>
+        <v>146.4</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -4185,13 +4185,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>81.583</v>
+        <v>83.239</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.949</v>
+        <v>-13.067</v>
       </c>
     </row>
     <row r="21">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -4262,13 +4262,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>78.52</v>
+        <v>79.871</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.493</v>
+        <v>-23.671</v>
       </c>
     </row>
     <row r="22">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -4339,13 +4339,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>130.51</v>
+        <v>128.779</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.221</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="23">
@@ -4366,22 +4366,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MRVL, MU</t>
+          <t>ADI, NOW</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MRVL: 2026-09-17 | MU: 2026-09-16</t>
+          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MRVL: -0.02% / +0.00% / 0.00% | MU: +5.48% / +6.44% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>6.752239299334195</v>
+        <v>10.31363400333991</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -4405,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.5</v>
+        <v>164.8</v>
       </c>
       <c r="O23" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -4428,13 +4428,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>24.858</v>
+        <v>26.484</v>
       </c>
       <c r="V23" t="n">
-        <v>19.426</v>
+        <v>23.41</v>
       </c>
       <c r="W23" t="n">
-        <v>-11.181</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="24">
@@ -4455,22 +4455,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>APH, COP</t>
+          <t>AMZN, APH</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>APH: 2026-09-14 | COP: 2026-09-17</t>
+          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>APH: -0.25% / +0.75% / -2.30% | COP: -0.02% / +0.00% / 0.00%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4209968749445014</v>
+        <v>-0.1230632240592611</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -4494,10 +4494,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N24" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="O24" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -4517,13 +4517,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="V24" t="n">
-        <v>49.157</v>
+        <v>48.349</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.175</v>
+        <v>-11.983</v>
       </c>
     </row>
     <row r="25">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="O25" t="n">
         <v>45.8</v>
@@ -4594,13 +4594,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>36.485</v>
+        <v>36.688</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.36</v>
+        <v>-3.365</v>
       </c>
     </row>
     <row r="26">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -4660,13 +4660,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N26" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O26" t="n">
         <v>69</v>
       </c>
       <c r="P26" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4683,13 +4683,13 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V26" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -4749,13 +4749,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N27" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O27" t="n">
         <v>69</v>
       </c>
       <c r="P27" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4772,13 +4772,13 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V27" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +13.01% / +20.81% / 0.00% | SMCI: +28.23% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>31.11411253223759</v>
+        <v>34.39118746217955</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -4838,13 +4838,13 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N28" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="O28" t="n">
         <v>69</v>
       </c>
       <c r="P28" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4861,13 +4861,13 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="V28" t="n">
-        <v>86.517</v>
+        <v>91.179</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.075</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -1131,14 +1131,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>10.31363400333991</v>
+        <v>10.48962615240752</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -1170,13 +1170,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>26.484</v>
+        <v>26.686</v>
       </c>
       <c r="V8" t="n">
-        <v>23.41</v>
+        <v>23.607</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.877</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="9">
@@ -1368,14 +1368,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1230632240592611</v>
+        <v>-0.1103226261906398</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -1407,13 +1407,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="V11" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.983</v>
+        <v>-11.964</v>
       </c>
     </row>
     <row r="12">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -1494,10 +1494,10 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V12" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -1581,10 +1581,10 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V13" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -1668,10 +1668,10 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V14" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>10.31363400333991</v>
+        <v>10.48962615240752</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -2266,13 +2266,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>26.484</v>
+        <v>26.686</v>
       </c>
       <c r="V23" t="n">
-        <v>23.41</v>
+        <v>23.607</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.877</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="24">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1230632240592611</v>
+        <v>-0.1103226261906398</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -2355,13 +2355,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="V24" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.983</v>
+        <v>-11.964</v>
       </c>
     </row>
     <row r="25">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -2521,10 +2521,10 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V26" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -2610,10 +2610,10 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V27" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2660,14 +2660,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -2699,10 +2699,10 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V28" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>10.31363400333991</v>
+        <v>10.48962615240752</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -3332,13 +3332,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>26.484</v>
+        <v>26.686</v>
       </c>
       <c r="V8" t="n">
-        <v>23.41</v>
+        <v>23.607</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.877</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="9">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1230632240592611</v>
+        <v>-0.1103226261906398</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -3569,13 +3569,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="V11" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.983</v>
+        <v>-11.964</v>
       </c>
     </row>
     <row r="12">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -3656,10 +3656,10 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V12" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3704,14 +3704,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -3743,10 +3743,10 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V13" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3791,14 +3791,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -3830,10 +3830,10 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V14" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -4389,14 +4389,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.29% / +3.46% / 0.00%</t>
+          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>10.31363400333991</v>
+        <v>10.48962615240752</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -4428,13 +4428,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>26.484</v>
+        <v>26.686</v>
       </c>
       <c r="V23" t="n">
-        <v>23.41</v>
+        <v>23.607</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.877</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="24">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.72% / +2.86% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1230632240592611</v>
+        <v>-0.1103226261906398</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -4517,13 +4517,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="V24" t="n">
-        <v>48.349</v>
+        <v>48.368</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.983</v>
+        <v>-11.964</v>
       </c>
     </row>
     <row r="25">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -4683,10 +4683,10 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V26" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -4772,10 +4772,10 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V27" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +17.28% / +20.81% / 0.00% | SMCI: +30.03% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>34.39118746217955</v>
+        <v>34.95477498872697</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -4861,10 +4861,10 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="V28" t="n">
-        <v>91.179</v>
+        <v>91.98</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -578,7 +578,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -783,13 +783,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>169.096</v>
+        <v>166.687</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.209</v>
+        <v>-23.001</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -858,13 +858,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>79.871</v>
+        <v>79.471</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-23.671</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60.3</v>
+        <v>60.1</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -933,13 +933,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>128.779</v>
+        <v>126.171</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.22</v>
+        <v>-0.217</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>147.4</v>
+        <v>147.1</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -1008,13 +1008,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>85.517</v>
+        <v>84.238</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.23</v>
+        <v>-13.139</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -1083,13 +1083,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>79.871</v>
+        <v>79.471</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-23.671</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="8">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1131,14 +1131,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
+          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>10.48962615240752</v>
+        <v>10.1400718997541</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -1147,10 +1147,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.8</v>
+        <v>164.5</v>
       </c>
       <c r="O8" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -1170,13 +1170,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>26.686</v>
+        <v>24.15</v>
       </c>
       <c r="V8" t="n">
-        <v>23.607</v>
+        <v>23.216</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.675</v>
+        <v>-6.957</v>
       </c>
     </row>
     <row r="9">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1245,13 +1245,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>36.688</v>
+        <v>36.497</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.365</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="10">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>146.4</v>
+        <v>146.1</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -1320,13 +1320,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>83.239</v>
+        <v>81.976</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.067</v>
+        <v>-12.977</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1368,14 +1368,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
+          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1103226261906398</v>
+        <v>0.05787671554968732</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -1407,13 +1407,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="V11" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.964</v>
+        <v>-11.715</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -1477,7 +1477,7 @@
         <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="13">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -1564,7 +1564,7 @@
         <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1581,13 +1581,13 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="14">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -1651,7 +1651,7 @@
         <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1668,13 +1668,13 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="16">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -1869,13 +1869,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>169.096</v>
+        <v>166.687</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.209</v>
+        <v>-23.001</v>
       </c>
     </row>
     <row r="19">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>147.4</v>
+        <v>147.1</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -1946,13 +1946,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>85.517</v>
+        <v>84.238</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-13.23</v>
+        <v>-13.139</v>
       </c>
     </row>
     <row r="20">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>146.4</v>
+        <v>146.1</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -2023,13 +2023,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>83.239</v>
+        <v>81.976</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-13.067</v>
+        <v>-12.977</v>
       </c>
     </row>
     <row r="21">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -2100,13 +2100,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>79.871</v>
+        <v>79.471</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.671</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="22">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60.3</v>
+        <v>60.1</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -2177,13 +2177,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>128.779</v>
+        <v>126.171</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.22</v>
+        <v>-0.217</v>
       </c>
     </row>
     <row r="23">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
+          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>10.48962615240752</v>
+        <v>10.1400718997541</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -2243,10 +2243,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.8</v>
+        <v>164.5</v>
       </c>
       <c r="O23" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -2266,13 +2266,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>26.686</v>
+        <v>24.15</v>
       </c>
       <c r="V23" t="n">
-        <v>23.607</v>
+        <v>23.216</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.675</v>
+        <v>-6.957</v>
       </c>
     </row>
     <row r="24">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
+          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1103226261906398</v>
+        <v>0.05787671554968732</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -2355,13 +2355,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="V24" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.964</v>
+        <v>-11.715</v>
       </c>
     </row>
     <row r="25">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2432,13 +2432,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>36.688</v>
+        <v>36.497</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.365</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="26">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -2504,7 +2504,7 @@
         <v>69</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2521,13 +2521,13 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="27">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -2593,7 +2593,7 @@
         <v>69</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2610,13 +2610,13 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="28">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -2682,7 +2682,7 @@
         <v>69</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2699,13 +2699,13 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
   </sheetData>
@@ -2740,7 +2740,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -2945,13 +2945,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>169.096</v>
+        <v>166.687</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.209</v>
+        <v>-23.001</v>
       </c>
     </row>
     <row r="4">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -3020,13 +3020,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>79.871</v>
+        <v>79.471</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-23.671</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="5">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60.3</v>
+        <v>60.1</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -3095,13 +3095,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>128.779</v>
+        <v>126.171</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.22</v>
+        <v>-0.217</v>
       </c>
     </row>
     <row r="6">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>147.4</v>
+        <v>147.1</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -3170,13 +3170,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>85.517</v>
+        <v>84.238</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.23</v>
+        <v>-13.139</v>
       </c>
     </row>
     <row r="7">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -3245,13 +3245,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>79.871</v>
+        <v>79.471</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-23.671</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="8">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
+          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>10.48962615240752</v>
+        <v>10.1400718997541</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -3309,10 +3309,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.8</v>
+        <v>164.5</v>
       </c>
       <c r="O8" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -3332,13 +3332,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>26.686</v>
+        <v>24.15</v>
       </c>
       <c r="V8" t="n">
-        <v>23.607</v>
+        <v>23.216</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.675</v>
+        <v>-6.957</v>
       </c>
     </row>
     <row r="9">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3407,13 +3407,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>36.688</v>
+        <v>36.497</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.365</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="10">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>146.4</v>
+        <v>146.1</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -3482,13 +3482,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>83.239</v>
+        <v>81.976</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.067</v>
+        <v>-12.977</v>
       </c>
     </row>
     <row r="11">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
+          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1103226261906398</v>
+        <v>0.05787671554968732</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -3569,13 +3569,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="V11" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.964</v>
+        <v>-11.715</v>
       </c>
     </row>
     <row r="12">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -3639,7 +3639,7 @@
         <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3656,13 +3656,13 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="13">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -3726,7 +3726,7 @@
         <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3743,13 +3743,13 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="14">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -3813,7 +3813,7 @@
         <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3830,13 +3830,13 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="16">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4008,7 +4008,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -4031,13 +4031,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>169.096</v>
+        <v>166.687</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.209</v>
+        <v>-23.001</v>
       </c>
     </row>
     <row r="19">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>147.4</v>
+        <v>147.1</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -4108,13 +4108,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>85.517</v>
+        <v>84.238</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-13.23</v>
+        <v>-13.139</v>
       </c>
     </row>
     <row r="20">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>146.4</v>
+        <v>146.1</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -4185,13 +4185,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>83.239</v>
+        <v>81.976</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-13.067</v>
+        <v>-12.977</v>
       </c>
     </row>
     <row r="21">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -4262,13 +4262,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>79.871</v>
+        <v>79.471</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.671</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="22">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60.3</v>
+        <v>60.1</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -4339,13 +4339,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>128.779</v>
+        <v>126.171</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.22</v>
+        <v>-0.217</v>
       </c>
     </row>
     <row r="23">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: -0.02% / +0.00% / 0.00% | NOW: +1.61% / +3.46% / 0.00%</t>
+          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>10.48962615240752</v>
+        <v>10.1400718997541</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -4405,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.8</v>
+        <v>164.5</v>
       </c>
       <c r="O23" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -4428,13 +4428,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>26.686</v>
+        <v>24.15</v>
       </c>
       <c r="V23" t="n">
-        <v>23.607</v>
+        <v>23.216</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.675</v>
+        <v>-6.957</v>
       </c>
     </row>
     <row r="24">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +2.74% / +3.37% / -2.30%</t>
+          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1103226261906398</v>
+        <v>0.05787671554968732</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -4517,13 +4517,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="V24" t="n">
-        <v>48.368</v>
+        <v>48.618</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.964</v>
+        <v>-11.715</v>
       </c>
     </row>
     <row r="25">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4594,13 +4594,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>36.688</v>
+        <v>36.497</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.365</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="26">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -4666,7 +4666,7 @@
         <v>69</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4683,13 +4683,13 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="27">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -4755,7 +4755,7 @@
         <v>69</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4772,13 +4772,13 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
     <row r="28">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +17.40% / +20.81% / 0.00% | SMCI: +30.93% / +34.49% / -1.72%</t>
+          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>34.95477498872697</v>
+        <v>34.08077432862746</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -4844,7 +4844,7 @@
         <v>69</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4861,13 +4861,13 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>91.98</v>
+        <v>90.73699999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>-1.282</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -1131,14 +1131,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
+          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>10.1400718997541</v>
+        <v>11.26897597381662</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -1170,13 +1170,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>24.15</v>
+        <v>25.422</v>
       </c>
       <c r="V8" t="n">
-        <v>23.216</v>
+        <v>24.479</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.957</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="9">
@@ -1368,14 +1368,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
+          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05787671554968732</v>
+        <v>0.5888595362702587</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -1407,13 +1407,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="V11" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.715</v>
+        <v>-10.926</v>
       </c>
     </row>
     <row r="12">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -1494,13 +1494,13 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V12" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -1581,13 +1581,13 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V13" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -1668,13 +1668,13 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V14" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
+          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>10.1400718997541</v>
+        <v>11.26897597381662</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -2266,13 +2266,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>24.15</v>
+        <v>25.422</v>
       </c>
       <c r="V23" t="n">
-        <v>23.216</v>
+        <v>24.479</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.957</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="24">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
+          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05787671554968732</v>
+        <v>0.5888595362702587</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -2355,13 +2355,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="V24" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.715</v>
+        <v>-10.926</v>
       </c>
     </row>
     <row r="25">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -2521,13 +2521,13 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V26" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -2610,13 +2610,13 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V27" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W27" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -2699,13 +2699,13 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V28" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W28" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
+          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>10.1400718997541</v>
+        <v>11.26897597381662</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -3332,13 +3332,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>24.15</v>
+        <v>25.422</v>
       </c>
       <c r="V8" t="n">
-        <v>23.216</v>
+        <v>24.479</v>
       </c>
       <c r="W8" t="n">
-        <v>-6.957</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="9">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
+          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05787671554968732</v>
+        <v>0.5888595362702587</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -3569,13 +3569,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="V11" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="W11" t="n">
-        <v>-11.715</v>
+        <v>-10.926</v>
       </c>
     </row>
     <row r="12">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -3656,13 +3656,13 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V12" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -3743,13 +3743,13 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V13" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -3830,13 +3830,13 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V14" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: +0.46% / +1.34% / -0.63% | NOW: +0.49% / +4.89% / -0.16%</t>
+          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>10.1400718997541</v>
+        <v>11.26897597381662</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -4428,13 +4428,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>24.15</v>
+        <v>25.422</v>
       </c>
       <c r="V23" t="n">
-        <v>23.216</v>
+        <v>24.479</v>
       </c>
       <c r="W23" t="n">
-        <v>-6.957</v>
+        <v>-5.684</v>
       </c>
     </row>
     <row r="24">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -1.59% / +0.21% / -1.80% | APH: +4.60% / +4.91% / -2.30%</t>
+          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05787671554968732</v>
+        <v>0.5888595362702587</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -4517,13 +4517,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="V24" t="n">
-        <v>48.618</v>
+        <v>49.407</v>
       </c>
       <c r="W24" t="n">
-        <v>-11.715</v>
+        <v>-10.926</v>
       </c>
     </row>
     <row r="25">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -4683,13 +4683,13 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V26" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -4772,13 +4772,13 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V27" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W27" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +17.76% / +20.81% / 0.00% | SMCI: +29.00% / +34.49% / -1.72%</t>
+          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>34.08077432862746</v>
+        <v>36.20230744385928</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -4861,13 +4861,13 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="V28" t="n">
-        <v>90.73699999999999</v>
+        <v>93.755</v>
       </c>
       <c r="W28" t="n">
-        <v>-1.282</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -783,13 +783,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>166.687</v>
+        <v>161.908</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.001</v>
+        <v>-22.589</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -858,13 +858,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>79.471</v>
+        <v>73.117</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-23.618</v>
+        <v>-22.782</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -933,13 +933,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>126.171</v>
+        <v>117.857</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.217</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>147.1</v>
+        <v>146.8</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -1008,13 +1008,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>84.238</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.139</v>
+        <v>-12.994</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -1083,13 +1083,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>79.471</v>
+        <v>73.117</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-23.618</v>
+        <v>-22.782</v>
       </c>
     </row>
     <row r="8">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ADI, NOW</t>
+          <t>ADI, AMD</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
+          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1131,14 +1131,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
+          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>11.26897597381662</v>
+        <v>11.04691393412145</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -1147,10 +1147,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.5</v>
+        <v>164.7</v>
       </c>
       <c r="O8" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -1170,13 +1170,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>25.422</v>
+        <v>24.85</v>
       </c>
       <c r="V8" t="n">
-        <v>24.479</v>
+        <v>24.23</v>
       </c>
       <c r="W8" t="n">
-        <v>-5.684</v>
+        <v>-5.919</v>
       </c>
     </row>
     <row r="9">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="O9" t="n">
         <v>45.8</v>
@@ -1245,13 +1245,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>36.497</v>
+        <v>33.406</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.36</v>
+        <v>-3.284</v>
       </c>
     </row>
     <row r="10">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>146.1</v>
+        <v>145.8</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -1320,13 +1320,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>81.976</v>
+        <v>79.974</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.977</v>
+        <v>-12.834</v>
       </c>
     </row>
     <row r="11">
@@ -1345,14 +1345,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>AMZN, APH</t>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
+          <t>AMZN: 2026-09-23 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1368,14 +1368,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5888595362702587</v>
+        <v>-1.074957659430154</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -1384,10 +1384,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="O11" t="n">
-        <v>64.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -1407,13 +1407,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="V11" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="W11" t="n">
-        <v>-10.926</v>
+        <v>-13.397</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -1477,7 +1477,7 @@
         <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V12" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -1564,7 +1564,7 @@
         <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V13" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -1651,7 +1651,7 @@
         <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V14" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -1869,13 +1869,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>166.687</v>
+        <v>161.908</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.001</v>
+        <v>-22.589</v>
       </c>
     </row>
     <row r="19">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>147.1</v>
+        <v>146.8</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -1946,13 +1946,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>84.238</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-13.139</v>
+        <v>-12.994</v>
       </c>
     </row>
     <row r="20">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>146.1</v>
+        <v>145.8</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -2023,13 +2023,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>81.976</v>
+        <v>79.974</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.977</v>
+        <v>-12.834</v>
       </c>
     </row>
     <row r="21">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -2100,13 +2100,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>79.471</v>
+        <v>73.117</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.618</v>
+        <v>-22.782</v>
       </c>
     </row>
     <row r="22">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -2177,13 +2177,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>126.171</v>
+        <v>117.857</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.217</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="23">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADI, NOW</t>
+          <t>ADI, AMD</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
+          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
+          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>11.26897597381662</v>
+        <v>11.04691393412145</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -2243,10 +2243,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.5</v>
+        <v>164.7</v>
       </c>
       <c r="O23" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -2266,13 +2266,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>25.422</v>
+        <v>24.85</v>
       </c>
       <c r="V23" t="n">
-        <v>24.479</v>
+        <v>24.23</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.684</v>
+        <v>-5.919</v>
       </c>
     </row>
     <row r="24">
@@ -2293,14 +2293,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>AMZN, APH</t>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
+          <t>AMZN: 2026-09-23 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5888595362702587</v>
+        <v>-1.074957659430154</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -2332,10 +2332,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N24" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="O24" t="n">
-        <v>64.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -2355,13 +2355,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="V24" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="W24" t="n">
-        <v>-10.926</v>
+        <v>-13.397</v>
       </c>
     </row>
     <row r="25">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="O25" t="n">
         <v>45.8</v>
@@ -2432,13 +2432,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>36.497</v>
+        <v>33.406</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.36</v>
+        <v>-3.284</v>
       </c>
     </row>
     <row r="26">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -2504,7 +2504,7 @@
         <v>69</v>
       </c>
       <c r="P26" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V26" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -2593,7 +2593,7 @@
         <v>69</v>
       </c>
       <c r="P27" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V27" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -2682,7 +2682,7 @@
         <v>69</v>
       </c>
       <c r="P28" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V28" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -2945,13 +2945,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>166.687</v>
+        <v>161.908</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-23.001</v>
+        <v>-22.589</v>
       </c>
     </row>
     <row r="4">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -3020,13 +3020,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>79.471</v>
+        <v>73.117</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-23.618</v>
+        <v>-22.782</v>
       </c>
     </row>
     <row r="5">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -3095,13 +3095,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>126.171</v>
+        <v>117.857</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.217</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="6">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>147.1</v>
+        <v>146.8</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -3170,13 +3170,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>84.238</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-13.139</v>
+        <v>-12.994</v>
       </c>
     </row>
     <row r="7">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -3245,13 +3245,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>79.471</v>
+        <v>73.117</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-23.618</v>
+        <v>-22.782</v>
       </c>
     </row>
     <row r="8">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ADI, NOW</t>
+          <t>ADI, AMD</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
+          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
+          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>11.26897597381662</v>
+        <v>11.04691393412145</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -3309,10 +3309,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.5</v>
+        <v>164.7</v>
       </c>
       <c r="O8" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -3332,13 +3332,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>25.422</v>
+        <v>24.85</v>
       </c>
       <c r="V8" t="n">
-        <v>24.479</v>
+        <v>24.23</v>
       </c>
       <c r="W8" t="n">
-        <v>-5.684</v>
+        <v>-5.919</v>
       </c>
     </row>
     <row r="9">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="O9" t="n">
         <v>45.8</v>
@@ -3407,13 +3407,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>36.497</v>
+        <v>33.406</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.36</v>
+        <v>-3.284</v>
       </c>
     </row>
     <row r="10">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>146.1</v>
+        <v>145.8</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -3482,13 +3482,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>81.976</v>
+        <v>79.974</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.977</v>
+        <v>-12.834</v>
       </c>
     </row>
     <row r="11">
@@ -3507,14 +3507,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>AMZN, APH</t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
+          <t>AMZN: 2026-09-23 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5888595362702587</v>
+        <v>-1.074957659430154</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -3546,10 +3546,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N11" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="O11" t="n">
-        <v>64.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -3569,13 +3569,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="V11" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="W11" t="n">
-        <v>-10.926</v>
+        <v>-13.397</v>
       </c>
     </row>
     <row r="12">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -3639,7 +3639,7 @@
         <v>69</v>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V12" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3681,12 +3681,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -3726,7 +3726,7 @@
         <v>69</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3743,10 +3743,10 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V13" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -3813,7 +3813,7 @@
         <v>69</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V14" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4008,7 +4008,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -4031,13 +4031,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>166.687</v>
+        <v>161.908</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-23.001</v>
+        <v>-22.589</v>
       </c>
     </row>
     <row r="19">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>147.1</v>
+        <v>146.8</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -4108,13 +4108,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>84.238</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-13.139</v>
+        <v>-12.994</v>
       </c>
     </row>
     <row r="20">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>146.1</v>
+        <v>145.8</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -4185,13 +4185,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>81.976</v>
+        <v>79.974</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.977</v>
+        <v>-12.834</v>
       </c>
     </row>
     <row r="21">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -4262,13 +4262,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>79.471</v>
+        <v>73.117</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-23.618</v>
+        <v>-22.782</v>
       </c>
     </row>
     <row r="22">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -4339,13 +4339,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>126.171</v>
+        <v>117.857</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.217</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="23">
@@ -4366,22 +4366,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADI, NOW</t>
+          <t>ADI, AMD</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | NOW: 2026-09-18</t>
+          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: +1.90% / +1.97% / -0.63% | NOW: +1.11% / +4.89% / -0.16%</t>
+          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>11.26897597381662</v>
+        <v>11.04691393412145</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -4405,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.5</v>
+        <v>164.7</v>
       </c>
       <c r="O23" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -4428,13 +4428,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>25.422</v>
+        <v>24.85</v>
       </c>
       <c r="V23" t="n">
-        <v>24.479</v>
+        <v>24.23</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.684</v>
+        <v>-5.919</v>
       </c>
     </row>
     <row r="24">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>AMZN, APH</t>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AMZN: 2026-09-21 | APH: 2026-09-14</t>
+          <t>AMZN: 2026-09-23 | APH: 2026-09-14</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -1.36% / +0.21% / -1.80% | APH: +5.44% / +6.14% / -2.30%</t>
+          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5888595362702587</v>
+        <v>-1.074957659430154</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -4494,10 +4494,10 @@
         <v>27.77777777777778</v>
       </c>
       <c r="N24" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="O24" t="n">
-        <v>64.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -4517,13 +4517,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="V24" t="n">
-        <v>49.407</v>
+        <v>46.936</v>
       </c>
       <c r="W24" t="n">
-        <v>-10.926</v>
+        <v>-13.397</v>
       </c>
     </row>
     <row r="25">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="O25" t="n">
         <v>45.8</v>
@@ -4594,13 +4594,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>36.497</v>
+        <v>33.406</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.36</v>
+        <v>-3.284</v>
       </c>
     </row>
     <row r="26">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -4666,7 +4666,7 @@
         <v>69</v>
       </c>
       <c r="P26" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V26" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -4755,7 +4755,7 @@
         <v>69</v>
       </c>
       <c r="P27" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V27" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +18.62% / +20.81% / 0.00% | SMCI: +32.01% / +34.49% / -1.72%</t>
+          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>36.20230744385928</v>
+        <v>38.25931014640187</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -4844,7 +4844,7 @@
         <v>69</v>
       </c>
       <c r="P28" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4861,10 +4861,10 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="V28" t="n">
-        <v>93.755</v>
+        <v>96.681</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>

--- a/ATL_usa.xlsx
+++ b/ATL_usa.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -760,7 +760,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -783,13 +783,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>161.908</v>
+        <v>159.084</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.589</v>
+        <v>-22.346</v>
       </c>
     </row>
     <row r="4">
@@ -808,12 +808,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -835,7 +835,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -858,13 +858,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>73.117</v>
+        <v>72.51300000000001</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.782</v>
+        <v>-22.702</v>
       </c>
     </row>
     <row r="5">
@@ -883,12 +883,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -933,13 +933,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>117.857</v>
+        <v>118.906</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.209</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="6">
@@ -958,12 +958,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>146.8</v>
+        <v>146.5</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -1008,13 +1008,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>82.20999999999999</v>
+        <v>82.746</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-12.994</v>
+        <v>-13.032</v>
       </c>
     </row>
     <row r="7">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -1083,13 +1083,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>73.117</v>
+        <v>72.51300000000001</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.782</v>
+        <v>-22.702</v>
       </c>
     </row>
     <row r="8">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ADI, AMD</t>
+          <t>AMD, ANET</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
+          <t>AMD: 2026-09-23 | ANET: 2026-09-24</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1131,14 +1131,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
+          <t>AMD: +1.59% / +2.32% / -2.48% | ANET: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>11.04691393412145</v>
+        <v>12.52531037061173</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -1147,10 +1147,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.7</v>
+        <v>164.9</v>
       </c>
       <c r="O8" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -1170,13 +1170,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>24.85</v>
+        <v>22.075</v>
       </c>
       <c r="V8" t="n">
-        <v>24.23</v>
+        <v>25.884</v>
       </c>
       <c r="W8" t="n">
-        <v>-5.919</v>
+        <v>-4.108</v>
       </c>
     </row>
     <row r="9">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="O9" t="n">
         <v>45.8</v>
@@ -1245,13 +1245,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>33.406</v>
+        <v>33.251</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.284</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="10">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>145.8</v>
+        <v>145.6</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -1320,13 +1320,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>79.974</v>
+        <v>80.502</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.834</v>
+        <v>-12.872</v>
       </c>
     </row>
     <row r="11">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1368,14 +1368,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
+          <t>AMZN: +0.03% / +0.19% / -1.47% | APH: +6.03% / +6.34% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.074957659430154</v>
+        <v>-0.3988439547068845</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -1387,7 +1387,7 @@
         <v>22.8</v>
       </c>
       <c r="O11" t="n">
-        <v>63</v>
+        <v>65.2</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -1407,13 +1407,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="V11" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="W11" t="n">
-        <v>-13.397</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="12">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -1494,10 +1494,10 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V12" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -1581,10 +1581,10 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V13" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1629,14 +1629,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -1668,10 +1668,10 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V14" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -1869,13 +1869,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>161.908</v>
+        <v>159.084</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-22.589</v>
+        <v>-22.346</v>
       </c>
     </row>
     <row r="19">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>146.8</v>
+        <v>146.5</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -1946,13 +1946,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>82.20999999999999</v>
+        <v>82.746</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.994</v>
+        <v>-13.032</v>
       </c>
     </row>
     <row r="20">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>145.8</v>
+        <v>145.6</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -2023,13 +2023,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>79.974</v>
+        <v>80.502</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.834</v>
+        <v>-12.872</v>
       </c>
     </row>
     <row r="21">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -2100,13 +2100,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>73.117</v>
+        <v>72.51300000000001</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-22.782</v>
+        <v>-22.702</v>
       </c>
     </row>
     <row r="22">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -2177,13 +2177,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>117.857</v>
+        <v>118.906</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.209</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="23">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADI, AMD</t>
+          <t>AMD, ANET</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
+          <t>AMD: 2026-09-23 | ANET: 2026-09-24</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
+          <t>AMD: +1.59% / +2.32% / -2.48% | ANET: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>11.04691393412145</v>
+        <v>12.52531037061173</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -2243,10 +2243,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.7</v>
+        <v>164.9</v>
       </c>
       <c r="O23" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -2266,13 +2266,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>24.85</v>
+        <v>22.075</v>
       </c>
       <c r="V23" t="n">
-        <v>24.23</v>
+        <v>25.884</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.919</v>
+        <v>-4.108</v>
       </c>
     </row>
     <row r="24">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
+          <t>AMZN: +0.03% / +0.19% / -1.47% | APH: +6.03% / +6.34% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.074957659430154</v>
+        <v>-0.3988439547068845</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -2335,7 +2335,7 @@
         <v>22.8</v>
       </c>
       <c r="O24" t="n">
-        <v>63</v>
+        <v>65.2</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -2355,13 +2355,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="V24" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="W24" t="n">
-        <v>-13.397</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="25">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="O25" t="n">
         <v>45.8</v>
@@ -2432,13 +2432,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>33.406</v>
+        <v>33.251</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.284</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="26">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2482,14 +2482,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -2521,10 +2521,10 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V26" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2571,14 +2571,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -2610,10 +2610,10 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V27" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -2699,10 +2699,10 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V28" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N3" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="O3" t="n">
         <v>51.8</v>
@@ -2945,13 +2945,13 @@
         <v>11.927</v>
       </c>
       <c r="U3" t="n">
-        <v>161.908</v>
+        <v>159.084</v>
       </c>
       <c r="V3" t="n">
         <v>134.662</v>
       </c>
       <c r="W3" t="n">
-        <v>-22.589</v>
+        <v>-22.346</v>
       </c>
     </row>
     <row r="4">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="O4" t="n">
         <v>48.4</v>
@@ -3020,13 +3020,13 @@
         <v>12.325</v>
       </c>
       <c r="U4" t="n">
-        <v>73.117</v>
+        <v>72.51300000000001</v>
       </c>
       <c r="V4" t="n">
         <v>66.072</v>
       </c>
       <c r="W4" t="n">
-        <v>-22.782</v>
+        <v>-22.702</v>
       </c>
     </row>
     <row r="5">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N5" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="O5" t="n">
         <v>54.5</v>
@@ -3095,13 +3095,13 @@
         <v>15.835</v>
       </c>
       <c r="U5" t="n">
-        <v>117.857</v>
+        <v>118.906</v>
       </c>
       <c r="V5" t="n">
         <v>106.833</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.209</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="6">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N6" t="n">
-        <v>146.8</v>
+        <v>146.5</v>
       </c>
       <c r="O6" t="n">
         <v>53.4</v>
@@ -3170,13 +3170,13 @@
         <v>8.715</v>
       </c>
       <c r="U6" t="n">
-        <v>82.20999999999999</v>
+        <v>82.746</v>
       </c>
       <c r="V6" t="n">
         <v>60.187</v>
       </c>
       <c r="W6" t="n">
-        <v>-12.994</v>
+        <v>-13.032</v>
       </c>
     </row>
     <row r="7">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N7" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="O7" t="n">
         <v>48.4</v>
@@ -3245,13 +3245,13 @@
         <v>12.325</v>
       </c>
       <c r="U7" t="n">
-        <v>73.117</v>
+        <v>72.51300000000001</v>
       </c>
       <c r="V7" t="n">
         <v>66.072</v>
       </c>
       <c r="W7" t="n">
-        <v>-22.782</v>
+        <v>-22.702</v>
       </c>
     </row>
     <row r="8">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ADI, AMD</t>
+          <t>AMD, ANET</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
+          <t>AMD: 2026-09-23 | ANET: 2026-09-24</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
+          <t>AMD: +1.59% / +2.32% / -2.48% | ANET: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K8" t="n">
-        <v>11.04691393412145</v>
+        <v>12.52531037061173</v>
       </c>
       <c r="L8" t="n">
         <v>18.40557264012871</v>
@@ -3309,10 +3309,10 @@
         <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>164.7</v>
+        <v>164.9</v>
       </c>
       <c r="O8" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="P8" t="n">
         <v>1.7</v>
@@ -3332,13 +3332,13 @@
         <v>23.406</v>
       </c>
       <c r="U8" t="n">
-        <v>24.85</v>
+        <v>22.075</v>
       </c>
       <c r="V8" t="n">
-        <v>24.23</v>
+        <v>25.884</v>
       </c>
       <c r="W8" t="n">
-        <v>-5.919</v>
+        <v>-4.108</v>
       </c>
     </row>
     <row r="9">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N9" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="O9" t="n">
         <v>45.8</v>
@@ -3407,13 +3407,13 @@
         <v>3.619</v>
       </c>
       <c r="U9" t="n">
-        <v>33.406</v>
+        <v>33.251</v>
       </c>
       <c r="V9" t="n">
         <v>30.326</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.284</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="10">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N10" t="n">
-        <v>145.8</v>
+        <v>145.6</v>
       </c>
       <c r="O10" t="n">
         <v>53.4</v>
@@ -3482,13 +3482,13 @@
         <v>8.715</v>
       </c>
       <c r="U10" t="n">
-        <v>79.974</v>
+        <v>80.502</v>
       </c>
       <c r="V10" t="n">
         <v>60.423</v>
       </c>
       <c r="W10" t="n">
-        <v>-12.834</v>
+        <v>-12.872</v>
       </c>
     </row>
     <row r="11">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
+          <t>AMZN: +0.03% / +0.19% / -1.47% | APH: +6.03% / +6.34% / -2.30%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.074957659430154</v>
+        <v>-0.3988439547068845</v>
       </c>
       <c r="L11" t="n">
         <v>3.457635521851321</v>
@@ -3549,7 +3549,7 @@
         <v>22.8</v>
       </c>
       <c r="O11" t="n">
-        <v>63</v>
+        <v>65.2</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -3569,13 +3569,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="V11" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="W11" t="n">
-        <v>-13.397</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="12">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K12" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L12" t="n">
         <v>7.879924557280349</v>
@@ -3656,10 +3656,10 @@
         <v>7.264</v>
       </c>
       <c r="U12" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V12" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -3681,12 +3681,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3704,14 +3704,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K13" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L13" t="n">
         <v>7.879924557280349</v>
@@ -3743,10 +3743,10 @@
         <v>7.264</v>
       </c>
       <c r="U13" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V13" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K14" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L14" t="n">
         <v>7.879924557280349</v>
@@ -3830,10 +3830,10 @@
         <v>7.264</v>
       </c>
       <c r="U14" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V14" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4008,7 +4008,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N18" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="O18" t="n">
         <v>51.8</v>
@@ -4031,13 +4031,13 @@
         <v>11.927</v>
       </c>
       <c r="U18" t="n">
-        <v>161.908</v>
+        <v>159.084</v>
       </c>
       <c r="V18" t="n">
         <v>134.662</v>
       </c>
       <c r="W18" t="n">
-        <v>-22.589</v>
+        <v>-22.346</v>
       </c>
     </row>
     <row r="19">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N19" t="n">
-        <v>146.8</v>
+        <v>146.5</v>
       </c>
       <c r="O19" t="n">
         <v>53.4</v>
@@ -4108,13 +4108,13 @@
         <v>8.715</v>
       </c>
       <c r="U19" t="n">
-        <v>82.20999999999999</v>
+        <v>82.746</v>
       </c>
       <c r="V19" t="n">
         <v>60.187</v>
       </c>
       <c r="W19" t="n">
-        <v>-12.994</v>
+        <v>-13.032</v>
       </c>
     </row>
     <row r="20">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N20" t="n">
-        <v>145.8</v>
+        <v>145.6</v>
       </c>
       <c r="O20" t="n">
         <v>53.4</v>
@@ -4185,13 +4185,13 @@
         <v>8.715</v>
       </c>
       <c r="U20" t="n">
-        <v>79.974</v>
+        <v>80.502</v>
       </c>
       <c r="V20" t="n">
         <v>60.423</v>
       </c>
       <c r="W20" t="n">
-        <v>-12.834</v>
+        <v>-12.872</v>
       </c>
     </row>
     <row r="21">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N21" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="O21" t="n">
         <v>48.4</v>
@@ -4262,13 +4262,13 @@
         <v>12.325</v>
       </c>
       <c r="U21" t="n">
-        <v>73.117</v>
+        <v>72.51300000000001</v>
       </c>
       <c r="V21" t="n">
         <v>66.072</v>
       </c>
       <c r="W21" t="n">
-        <v>-22.782</v>
+        <v>-22.702</v>
       </c>
     </row>
     <row r="22">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
         <v>94.44444444444444</v>
       </c>
       <c r="N22" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="O22" t="n">
         <v>54.5</v>
@@ -4339,13 +4339,13 @@
         <v>15.835</v>
       </c>
       <c r="U22" t="n">
-        <v>117.857</v>
+        <v>118.906</v>
       </c>
       <c r="V22" t="n">
         <v>106.833</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.209</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="23">
@@ -4366,22 +4366,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ADI, AMD</t>
+          <t>AMD, ANET</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ADI: 2026-09-21 | AMD: 2026-09-23</t>
+          <t>AMD: 2026-09-23 | ANET: 2026-09-24</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADI: -0.69% / +1.97% / -1.04% | AMD: -0.02% / +0.00% / 0.00%</t>
+          <t>AMD: +1.59% / +2.32% / -2.48% | ANET: -0.02% / +0.00% / 0.00%</t>
         </is>
       </c>
       <c r="J23" t="n">
         <v>9.984988963105934</v>
       </c>
       <c r="K23" t="n">
-        <v>11.04691393412145</v>
+        <v>12.52531037061173</v>
       </c>
       <c r="L23" t="n">
         <v>18.40557264012871</v>
@@ -4405,10 +4405,10 @@
         <v>100</v>
       </c>
       <c r="N23" t="n">
-        <v>164.7</v>
+        <v>164.9</v>
       </c>
       <c r="O23" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="P23" t="n">
         <v>1.7</v>
@@ -4428,13 +4428,13 @@
         <v>23.406</v>
       </c>
       <c r="U23" t="n">
-        <v>24.85</v>
+        <v>22.075</v>
       </c>
       <c r="V23" t="n">
-        <v>24.23</v>
+        <v>25.884</v>
       </c>
       <c r="W23" t="n">
-        <v>-5.919</v>
+        <v>-4.108</v>
       </c>
     </row>
     <row r="24">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AMZN: -0.02% / +0.00% / 0.00% | APH: +4.73% / +6.16% / -2.30%</t>
+          <t>AMZN: +0.03% / +0.19% / -1.47% | APH: +6.03% / +6.34% / -2.30%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>7.003547098247198</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.074957659430154</v>
+        <v>-0.3988439547068845</v>
       </c>
       <c r="L24" t="n">
         <v>3.457635521851321</v>
@@ -4497,7 +4497,7 @@
         <v>22.8</v>
       </c>
       <c r="O24" t="n">
-        <v>63</v>
+        <v>65.2</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
@@ -4517,13 +4517,13 @@
         <v>8.563000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="V24" t="n">
-        <v>46.936</v>
+        <v>47.94</v>
       </c>
       <c r="W24" t="n">
-        <v>-13.397</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="25">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
         <v>88.88888888888889</v>
       </c>
       <c r="N25" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="O25" t="n">
         <v>45.8</v>
@@ -4594,13 +4594,13 @@
         <v>3.619</v>
       </c>
       <c r="U25" t="n">
-        <v>33.406</v>
+        <v>33.251</v>
       </c>
       <c r="V25" t="n">
         <v>30.326</v>
       </c>
       <c r="W25" t="n">
-        <v>-3.284</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="26">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4644,14 +4644,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K26" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L26" t="n">
         <v>7.879924557280349</v>
@@ -4683,10 +4683,10 @@
         <v>7.264</v>
       </c>
       <c r="U26" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V26" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K27" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L27" t="n">
         <v>7.879924557280349</v>
@@ -4772,10 +4772,10 @@
         <v>7.264</v>
       </c>
       <c r="U27" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V27" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLTR: +22.48% / +24.29% / 0.00% | SMCI: +31.99% / +35.73% / -1.72%</t>
+          <t>PLTR: +23.79% / +24.86% / 0.00% | SMCI: +31.92% / +35.73% / -1.72%</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>-2.485427299932685</v>
       </c>
       <c r="K28" t="n">
-        <v>38.25931014640187</v>
+        <v>38.92003623083748</v>
       </c>
       <c r="L28" t="n">
         <v>7.879924557280349</v>
@@ -4861,10 +4861,10 @@
         <v>7.264</v>
       </c>
       <c r="U28" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="V28" t="n">
-        <v>96.681</v>
+        <v>97.621</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
